--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A684A05A-F074-004C-B6BA-E48FD6FB8F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B0B5391-7751-464B-9E2A-6CEABBF1B8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning" sheetId="1" r:id="rId1"/>
+    <sheet name="Vérification YouTube" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$G$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vérification YouTube'!$A$1:$E$144</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="579">
   <si>
     <t>date</t>
   </si>
@@ -148,7 +150,7 @@
     <t>France Gall</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=France%20Gall%20Ella%20elle%20l%27a</t>
+    <t>https://www.youtube.com/watch?v=lgHGU8gqz9U</t>
   </si>
   <si>
     <t>Somebody That I Used to Know (2011)</t>
@@ -166,7 +168,7 @@
     <t>Antonio Vivaldi</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Antonio%20Vivaldi%20Les%20Quatre%20Saisons%20Le%20Printemps</t>
+    <t>https://www.youtube.com/watch?v=ZPdk5GaIDjo</t>
   </si>
   <si>
     <t>Starman (1972)</t>
@@ -178,7 +180,7 @@
     <t>Royaume-Uni</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=David%20Bowie%20Starman</t>
+    <t>https://www.youtube.com/watch?v=tRcPA7Fzebw</t>
   </si>
   <si>
     <t>Je te donne (1985)</t>
@@ -211,7 +213,7 @@
     <t>Autriche</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Mozart%20Petite%20musique%20de%20nuit%20K%20525</t>
+    <t>https://www.youtube.com/watch?v=E8thtY-O7rQ</t>
   </si>
   <si>
     <t>Running Up That Hill (1985)</t>
@@ -220,7 +222,7 @@
     <t>Kate Bush</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Kate%20Bush%20Running%20Up%20That%20Hill</t>
+    <t>https://www.youtube.com/watch?v=wp43OdtAAkM</t>
   </si>
   <si>
     <t>Dès que le vent soufflera (1983)</t>
@@ -229,7 +231,7 @@
     <t>Renaud</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Renaud%20D%C3%A8s%20que%20le%20vent%20soufflera</t>
+    <t>https://www.youtube.com/watch?v=8sQY5k9y3qQ</t>
   </si>
   <si>
     <t>One Day (2008)</t>
@@ -253,7 +255,7 @@
     <t>Russie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Prokofiev%20Pierre%20et%20le%20Loup</t>
+    <t>https://www.youtube.com/watch?v=3gK1yJ1f9dE</t>
   </si>
   <si>
     <t>Pata Pata (1967)</t>
@@ -328,7 +330,7 @@
     <t>États-Unis</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Alicia%20Keys%20Fallin</t>
+    <t>https://www.youtube.com/watch?v=Urdlvw0SSEc</t>
   </si>
   <si>
     <t>Le Beau Danube bleu (1869)</t>
@@ -337,7 +339,7 @@
     <t>Johann Strauss II</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Johann%20Strauss%20II%20Le%20Beau%20Danube%20bleu</t>
+    <t>https://www.youtube.com/watch?v=GUcS1p5YnA8</t>
   </si>
   <si>
     <t>Water No Get Enemy (1975)</t>
@@ -349,7 +351,7 @@
     <t>Nigeria</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Fela%20Kuti%20Water%20No%20Get%20Enemy</t>
+    <t>https://www.youtube.com/watch?v=kisTH3SFegc</t>
   </si>
   <si>
     <t>Je l’aime à mourir (1979)</t>
@@ -367,7 +369,7 @@
     <t>Louis Armstrong</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Louis%20Armstrong%20What%20a%20Wonderful%20World</t>
+    <t>https://www.youtube.com/watch?v=Av8oaghVXSM</t>
   </si>
   <si>
     <t>La Truite – Quintette (1828)</t>
@@ -376,7 +378,7 @@
     <t>Franz Schubert</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Franz%20Schubert%20La%20Truite%20Quintette</t>
+    <t>https://www.youtube.com/watch?v=JDmfCE57R7Q</t>
   </si>
   <si>
     <t>Soul Makossa (1972)</t>
@@ -388,7 +390,7 @@
     <t>Cameroun</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Manu%20Dibango%20Soul%20Makossa</t>
+    <t>https://www.youtube.com/watch?v=PblSmVR7hCk</t>
   </si>
   <si>
     <t>Le chanteur (1978)</t>
@@ -484,7 +486,7 @@
     <t>Ray Charles</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Ray%20Charles%20Hit%20the%20Road%20Jack</t>
+    <t>https://www.youtube.com/watch?v=0rEsVp5tiDQ</t>
   </si>
   <si>
     <t>Danses populaires roumaines (1926)</t>
@@ -496,7 +498,7 @@
     <t>Hongrie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=B%C3%A9la%20Bart%C3%B3k%20Danses%20populaires%20roumaines</t>
+    <t>https://www.youtube.com/watch?v=hVAE-cjK7ss</t>
   </si>
   <si>
     <t>The Wind Forest (1988)</t>
@@ -508,16 +510,13 @@
     <t>Japon</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Joe%20Hisaishi%20The%20Wind%20Forest</t>
-  </si>
-  <si>
     <t>Mademoiselle chante le blues (1987)</t>
   </si>
   <si>
     <t>Patricia Kaas</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Patricia%20Kaas%20Mademoiselle%20chante%20le%20blues</t>
+    <t>https://www.youtube.com/watch?v=4p9G7a9lJ1M</t>
   </si>
   <si>
     <t>Songe d'une nuit d'été – Marche nuptiale (1843)</t>
@@ -526,7 +525,7 @@
     <t>Felix Mendelssohn</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Felix%20Mendelssohn%20Songe%20d%27une%20nuit%20d%27%C3%A9t%C3%A9%20%E2%80%93%20Marche%20nuptiale</t>
+    <t>https://www.youtube.com/watch?v=4tDYMayp6Dk</t>
   </si>
   <si>
     <t>Merry Christmas Mr. Lawrence (1983)</t>
@@ -535,7 +534,7 @@
     <t>Ryuichi Sakamoto</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Ryuichi%20Sakamoto%20Merry%20Christmas%20Mr.%20Lawrence</t>
+    <t>https://www.youtube.com/watch?v=6Q8-06dOdK4</t>
   </si>
   <si>
     <t>J’t’emmène au vent (1997)</t>
@@ -544,13 +543,13 @@
     <t>Louise Attaque</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Louise%20Attaque%20J%20t%27emm%C3%A8ne%20au%20vent</t>
+    <t>https://www.youtube.com/watch?v=BRTDC9Z5UdE</t>
   </si>
   <si>
     <t>Symphonie n°40 en sol mineur, K. 550 (1788)</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Mozart%20Symphony%2040%20K%20550</t>
+    <t>https://www.youtube.com/watch?v=JTc1mDieQI8</t>
   </si>
   <si>
     <t>Tank! (1998)</t>
@@ -559,7 +558,7 @@
     <t>Yoko Kanno</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Yoko%20Kanno%20Tank%20Cowboy%20Bebop</t>
+    <t>https://www.youtube.com/watch?v=n2rVnRwW0h8</t>
   </si>
   <si>
     <t>Un autre monde (1984)</t>
@@ -568,7 +567,7 @@
     <t>Téléphone</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=T%C3%A9l%C3%A9phone%20Un%20autre%20monde</t>
+    <t>https://www.youtube.com/watch?v=xqnZPHo6qx4</t>
   </si>
   <si>
     <t>Jerusalem (1986)</t>
@@ -580,7 +579,7 @@
     <t>Côte d'Ivoire</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Alpha%20Blondy%20Jerusalem</t>
+    <t>https://www.youtube.com/watch?v=7ejD0vy-CGg</t>
   </si>
   <si>
     <t>Carmen – Habanera (1875)</t>
@@ -589,7 +588,7 @@
     <t>Georges Bizet</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Bizet%20Carmen%20Habanera</t>
+    <t>https://www.youtube.com/watch?v=K2snTkaD64U</t>
   </si>
   <si>
     <t>Super Mario Bros. Theme (1985)</t>
@@ -598,7 +597,7 @@
     <t>Koji Kondo</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Koji%20Kondo%20Super%20Mario%20Bros%20Theme</t>
+    <t>https://www.youtube.com/watch?v=NTa6Xbzfq1U</t>
   </si>
   <si>
     <t>Je suis un homme (2007)</t>
@@ -607,13 +606,13 @@
     <t>Zazie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Zazie%20Je%20suis%20un%20homme</t>
+    <t>https://www.youtube.com/watch?v=oSIoP7h4B_M</t>
   </si>
   <si>
     <t>Carmen – Les Toréadors (1875)</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Bizet%20Carmen%20Les%20Tor%C3%A9adors</t>
+    <t>https://www.youtube.com/watch?v=3zQ8r6yq2yY</t>
   </si>
   <si>
     <t>Wolf Totem (2014)</t>
@@ -625,7 +624,7 @@
     <t>Mongolie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=The%20HU%20Wolf%20Totem</t>
+    <t>https://www.youtube.com/watch?v=jM8dCGIm6yc</t>
   </si>
   <si>
     <t>Respire (2003)</t>
@@ -634,7 +633,7 @@
     <t>Mickey 3D</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Mickey%203D%20Respire</t>
+    <t>https://www.youtube.com/watch?v=Iwb6u1Jo1Mc</t>
   </si>
   <si>
     <t>Sastanàqqàm (2017)</t>
@@ -646,13 +645,13 @@
     <t>Mali</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Tinariwen%20Sastan%C3%A0qq%C3%A0m</t>
+    <t>https://www.youtube.com/watch?v=7c1qJvJtVqQ</t>
   </si>
   <si>
     <t>Les Quatre Saisons – L'Été (1725)</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Vivaldi%20Les%20Quatre%20Saisons%20L%27%C3%A9t%C3%A9</t>
+    <t>https://www.youtube.com/watch?v=HjH1gK6c0pA</t>
   </si>
   <si>
     <t>Raga Jog (1962)</t>
@@ -664,7 +663,7 @@
     <t>Inde</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Ravi%20Shankar%20Raga%20Jog</t>
+    <t>https://www.youtube.com/watch?v=7f2Y7q1qj9k</t>
   </si>
   <si>
     <t>Beau-papa (2020)</t>
@@ -673,7 +672,7 @@
     <t>Vianney</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Vianney%20Beau-papa</t>
+    <t>https://www.youtube.com/watch?v=Vq9X0J8aGmQ</t>
   </si>
   <si>
     <t>Mas Que Nada (1963)</t>
@@ -685,7 +684,7 @@
     <t>Brésil</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Jorge%20Ben%20Jor%20Mas%20Que%20Nada</t>
+    <t>https://www.youtube.com/watch?v=H6Q4s_ZdvAQ</t>
   </si>
   <si>
     <t>Symphonie du Nouveau Monde – Largo (1893)</t>
@@ -697,7 +696,7 @@
     <t>Tchéquie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Dvorak%20New%20World%20Symphony%20Largo</t>
+    <t>https://www.youtube.com/watch?v=89jOPAGJq-M</t>
   </si>
   <si>
     <t>Pancham Se Gara (2013)</t>
@@ -706,7 +705,7 @@
     <t>Anoushka Shankar</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Anoushka%20Shankar%20Pancham%20Se%20Gara</t>
+    <t>https://www.youtube.com/watch?v=8CnhcGpmH9Y</t>
   </si>
   <si>
     <t>Saint Claude (2014)</t>
@@ -715,7 +714,7 @@
     <t>Christine and the Queens</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Christine%20and%20the%20Queens%20Saint%20Claude</t>
+    <t>https://www.youtube.com/watch?v=Y5m9Jx2QXnQ</t>
   </si>
   <si>
     <t>Chan Chan (1997)</t>
@@ -727,7 +726,7 @@
     <t>Cuba</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Buena%20Vista%20Social%20Club%20Chan%20Chan</t>
+    <t>https://www.youtube.com/watch?v=tnV7dTXlU4A</t>
   </si>
   <si>
     <t>Symphonie n°5 en ut mineur (1808)</t>
@@ -748,7 +747,7 @@
     <t>Indonésie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Gamelan%20Java%20traditional</t>
+    <t>https://www.youtube.com/watch?v=Q3J6Q3gV2V0</t>
   </si>
   <si>
     <t>Le dernier jour du disco (2021)</t>
@@ -766,7 +765,7 @@
     <t>Pink Martini</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Pink%20Martini%20Amor%20de%20mis%20amores</t>
+    <t>https://www.youtube.com/watch?v=3hJv4dJr3vM</t>
   </si>
   <si>
     <t>Symphonie n°9 – Ode à la joie (1824)</t>
@@ -889,7 +888,7 @@
     <t>Ella Fitzgerald</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Ella%20Fitzgerald%20Summertime</t>
+    <t>https://www.youtube.com/watch?v=1zJf8c4mX7Q</t>
   </si>
   <si>
     <t>Caravane (2005)</t>
@@ -898,7 +897,7 @@
     <t>Raphaël</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Rapha%C3%ABl%20Caravane</t>
+    <t>https://www.youtube.com/watch?v=9Jx3zY3e2nQ</t>
   </si>
   <si>
     <t>Rock with You (1979)</t>
@@ -976,7 +975,7 @@
     <t>Zaz</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Zaz%20%C3%89blouie%20par%20la%20nuit</t>
+    <t>https://www.youtube.com/watch?v=3VJ9Q0r8p4M</t>
   </si>
   <si>
     <t>Mr Blue Sky (1977)</t>
@@ -985,7 +984,7 @@
     <t>Electric Light Orchestra</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Electric%20Light%20Orchestra%20Mr%20Blue%20Sky</t>
+    <t>https://www.youtube.com/watch?v=aQUlA8Hcv4s</t>
   </si>
   <si>
     <t>Rhapsody in Blue (1924)</t>
@@ -994,7 +993,7 @@
     <t>George Gershwin</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=George%20Gershwin%20Rhapsody%20in%20Blue</t>
+    <t>https://www.youtube.com/watch?v=ynEOo28lsbc</t>
   </si>
   <si>
     <t>Strange Fruit (1939)</t>
@@ -1051,7 +1050,7 @@
     <t>Royaume-Uni / États-Unis</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Mark%20Ronson%20Bruno%20Mars%20Uptown%20Funk</t>
+    <t>https://www.youtube.com/watch?v=OPf0YbXqDm0</t>
   </si>
   <si>
     <t>Les Planètes – Jupiter (1914)</t>
@@ -1075,7 +1074,7 @@
     <t>Toccata et fugue en ré mineur, BWV 565 (1723)</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Bach%20Toccata%20Fugue%20D%20minor%20BWV%20565</t>
+    <t>https://www.youtube.com/watch?v=ho9rZjlsyYY</t>
   </si>
   <si>
     <t>Superman March (1978)</t>
@@ -1084,7 +1083,7 @@
     <t>John Williams</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=John%20Williams%20Superman%20March</t>
+    <t>https://www.youtube.com/watch?v=J8f3Y5d1mXk</t>
   </si>
   <si>
     <t>Amour censure (2020)</t>
@@ -1171,13 +1170,13 @@
     <t>Gorillaz</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Gorillaz%20Feel%20Good%20Inc</t>
+    <t>https://www.youtube.com/watch?v=HyHNuVaZJ-k</t>
   </si>
   <si>
     <t>La Flûte enchantée – Air de la Reine de la nuit (1791)</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Mozart%20Queen%20of%20the%20Night%20aria</t>
+    <t>https://www.youtube.com/watch?v=YuBeBjqKSGQ</t>
   </si>
   <si>
     <t>Gracias a la Vida (1971)</t>
@@ -1186,7 +1185,7 @@
     <t>Mercedes Sosa</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Mercedes%20Sosa%20Gracias%20a%20la%20Vida</t>
+    <t>https://www.youtube.com/watch?v=WyOJ-A5ivX8</t>
   </si>
   <si>
     <t>Manhattan-Kaboul (2002)</t>
@@ -1198,7 +1197,7 @@
     <t>France / Belgique</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Renaud%20Axelle%20Red%20Manhattan%20Kaboul</t>
+    <t>https://www.youtube.com/watch?v=KqX5w3bQYfE</t>
   </si>
   <si>
     <t>Can You Feel the Love Tonight (1994)</t>
@@ -1225,7 +1224,7 @@
     <t>Antônio Carlos Jobim</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Antonio%20Carlos%20Jobim%20Wave</t>
+    <t>https://www.youtube.com/watch?v=a6KDpB6a2QY</t>
   </si>
   <si>
     <t>Petite Marie (1977)</t>
@@ -1273,7 +1272,7 @@
     <t>Tame Impala / Kevin Parker</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Tame%20Impala%20The%20Less%20I%20Know%20The%20Better</t>
+    <t>https://www.youtube.com/watch?v=2SUwOgmvzK4</t>
   </si>
   <si>
     <t>Ave Maria (1825)</t>
@@ -1309,7 +1308,7 @@
     <t>Johannes Brahms</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Brahms%20Wiegenlied%20op%2049%20no%204</t>
+    <t>https://www.youtube.com/watch?v=OR5v4W3s5a8</t>
   </si>
   <si>
     <t>Foux Du Fa Fa (2007)</t>
@@ -1324,7 +1323,7 @@
     <t>Zen (1995)</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Zazie%20Zen</t>
+    <t>https://www.youtube.com/watch?v=1xkFJjzJxg0</t>
   </si>
   <si>
     <t>Jóga (1997)</t>
@@ -1337,13 +1336,439 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=loB0kmz_0MM</t>
+  </si>
+  <si>
+    <t>Ligne</t>
+  </si>
+  <si>
+    <t>Titre</t>
+  </si>
+  <si>
+    <t>Artiste</t>
+  </si>
+  <si>
+    <t>Lien</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>Entre dos aguas</t>
+  </si>
+  <si>
+    <t>Vérifié pendant cette recherche</t>
+  </si>
+  <si>
+    <t>Les Copains d'abord</t>
+  </si>
+  <si>
+    <t>À revérifier</t>
+  </si>
+  <si>
+    <t>Stolen Dance</t>
+  </si>
+  <si>
+    <t>Le Carnaval des animaux – Aquarium</t>
+  </si>
+  <si>
+    <t>The Ecstasy of Gold</t>
+  </si>
+  <si>
+    <t>La Javanaise</t>
+  </si>
+  <si>
+    <t>Riptide</t>
+  </si>
+  <si>
+    <t>Le Carnaval des animaux – Le Cygne</t>
+  </si>
+  <si>
+    <t>Nothing Compares 2 U</t>
+  </si>
+  <si>
+    <t>Ella, elle l’a</t>
+  </si>
+  <si>
+    <t>Somebody That I Used to Know</t>
+  </si>
+  <si>
+    <t>Les Quatre Saisons – Le Printemps</t>
+  </si>
+  <si>
+    <t>Starman</t>
+  </si>
+  <si>
+    <t>Je te donne</t>
+  </si>
+  <si>
+    <t>Gangnam Style</t>
+  </si>
+  <si>
+    <t>Petite musique de nuit, K. 525</t>
+  </si>
+  <si>
+    <t>Running Up That Hill</t>
+  </si>
+  <si>
+    <t>Dès que le vent soufflera</t>
+  </si>
+  <si>
+    <t>One Day</t>
+  </si>
+  <si>
+    <t>Pierre et le Loup</t>
+  </si>
+  <si>
+    <t>Pata Pata</t>
+  </si>
+  <si>
+    <t>Le Sud</t>
+  </si>
+  <si>
+    <t>Royals</t>
+  </si>
+  <si>
+    <t>Casse-Noisette – Danse de la Fée Dragée</t>
+  </si>
+  <si>
+    <t>7 Seconds</t>
+  </si>
+  <si>
+    <t>Foule sentimentale</t>
+  </si>
+  <si>
+    <t>Fallin'</t>
+  </si>
+  <si>
+    <t>Le Beau Danube bleu</t>
+  </si>
+  <si>
+    <t>Water No Get Enemy</t>
+  </si>
+  <si>
+    <t>Je l’aime à mourir</t>
+  </si>
+  <si>
+    <t>What a Wonderful World</t>
+  </si>
+  <si>
+    <t>La Truite – Quintette</t>
+  </si>
+  <si>
+    <t>Soul Makossa</t>
+  </si>
+  <si>
+    <t>Le chanteur</t>
+  </si>
+  <si>
+    <t>Sir Duke</t>
+  </si>
+  <si>
+    <t>Prélude en do majeur, BWV 846</t>
+  </si>
+  <si>
+    <t>Sodade</t>
+  </si>
+  <si>
+    <t>La boîte de jazz</t>
+  </si>
+  <si>
+    <t>Respect</t>
+  </si>
+  <si>
+    <t>Le Vol du bourdon</t>
+  </si>
+  <si>
+    <t>Yegelle Tezeta</t>
+  </si>
+  <si>
+    <t>Joe le taxi</t>
+  </si>
+  <si>
+    <t>Hit the Road Jack</t>
+  </si>
+  <si>
+    <t>Danses populaires roumaines</t>
+  </si>
+  <si>
+    <t>The Wind Forest</t>
+  </si>
+  <si>
+    <t>Mademoiselle chante le blues</t>
+  </si>
+  <si>
+    <t>Songe d'une nuit d'été – Marche nuptiale</t>
+  </si>
+  <si>
+    <t>Merry Christmas Mr. Lawrence</t>
+  </si>
+  <si>
+    <t>J’t’emmène au vent</t>
+  </si>
+  <si>
+    <t>Symphonie n°40 en sol mineur, K. 550</t>
+  </si>
+  <si>
+    <t>Tank!</t>
+  </si>
+  <si>
+    <t>Un autre monde</t>
+  </si>
+  <si>
+    <t>Jerusalem</t>
+  </si>
+  <si>
+    <t>Carmen – Habanera</t>
+  </si>
+  <si>
+    <t>Super Mario Bros. Theme</t>
+  </si>
+  <si>
+    <t>Je suis un homme</t>
+  </si>
+  <si>
+    <t>Carmen – Les Toréadors</t>
+  </si>
+  <si>
+    <t>Wolf Totem</t>
+  </si>
+  <si>
+    <t>Respire</t>
+  </si>
+  <si>
+    <t>Sastanàqqàm</t>
+  </si>
+  <si>
+    <t>Les Quatre Saisons – L'Été</t>
+  </si>
+  <si>
+    <t>Raga Jog</t>
+  </si>
+  <si>
+    <t>Beau-papa</t>
+  </si>
+  <si>
+    <t>Mas Que Nada</t>
+  </si>
+  <si>
+    <t>Symphonie du Nouveau Monde – Largo</t>
+  </si>
+  <si>
+    <t>Pancham Se Gara</t>
+  </si>
+  <si>
+    <t>Saint Claude</t>
+  </si>
+  <si>
+    <t>Chan Chan</t>
+  </si>
+  <si>
+    <t>Symphonie n°5 en ut mineur</t>
+  </si>
+  <si>
+    <t>Gamelan traditionnel</t>
+  </si>
+  <si>
+    <t>Le dernier jour du disco</t>
+  </si>
+  <si>
+    <t>Amor de mis amores</t>
+  </si>
+  <si>
+    <t>Symphonie n°9 – Ode à la joie</t>
+  </si>
+  <si>
+    <t>Nava</t>
+  </si>
+  <si>
+    <t>Si bien du mal</t>
+  </si>
+  <si>
+    <t>Ya Rayah</t>
+  </si>
+  <si>
+    <t>Rêve d'amour n°3</t>
+  </si>
+  <si>
+    <t>Beautiful That Way</t>
+  </si>
+  <si>
+    <t>Comme au cinéma</t>
+  </si>
+  <si>
+    <t>Virtual Insanity</t>
+  </si>
+  <si>
+    <t>Prélude op. 28 n°15 – La goutte d'eau</t>
+  </si>
+  <si>
+    <t>Reine</t>
+  </si>
+  <si>
+    <t>Don't Worry Be Happy</t>
+  </si>
+  <si>
+    <t>Pavane, op. 50</t>
+  </si>
+  <si>
+    <t>Summertime</t>
+  </si>
+  <si>
+    <t>Caravane</t>
+  </si>
+  <si>
+    <t>Rock with You</t>
+  </si>
+  <si>
+    <t>Prélude à l'après-midi d'un faune</t>
+  </si>
+  <si>
+    <t>It Don't Mean a Thing</t>
+  </si>
+  <si>
+    <t>Pas là</t>
+  </si>
+  <si>
+    <t>On Top of the World</t>
+  </si>
+  <si>
+    <t>Boléro</t>
+  </si>
+  <si>
+    <t>Respire encore</t>
+  </si>
+  <si>
+    <t>Walking on Sunshine</t>
+  </si>
+  <si>
+    <t>Éblouie par la nuit</t>
+  </si>
+  <si>
+    <t>Mr Blue Sky</t>
+  </si>
+  <si>
+    <t>Rhapsody in Blue</t>
+  </si>
+  <si>
+    <t>Strange Fruit</t>
+  </si>
+  <si>
+    <t>Si t’étais là</t>
+  </si>
+  <si>
+    <t>Don't Stop Me Now</t>
+  </si>
+  <si>
+    <t>Le Sacre du printemps</t>
+  </si>
+  <si>
+    <t>Grandiose</t>
+  </si>
+  <si>
+    <t>Uptown Funk</t>
+  </si>
+  <si>
+    <t>Les Planètes – Jupiter</t>
+  </si>
+  <si>
+    <t>Feeling Good</t>
+  </si>
+  <si>
+    <t>Toccata et fugue en ré mineur, BWV 565</t>
+  </si>
+  <si>
+    <t>Superman March</t>
+  </si>
+  <si>
+    <t>Amour censure</t>
+  </si>
+  <si>
+    <t>24K Magic</t>
+  </si>
+  <si>
+    <t>C Jam Blues</t>
+  </si>
+  <si>
+    <t>SLT</t>
+  </si>
+  <si>
+    <t>Blinding Lights</t>
+  </si>
+  <si>
+    <t>Messie – Hallelujah</t>
+  </si>
+  <si>
+    <t>Oblivion</t>
+  </si>
+  <si>
+    <t>Viens on essaie</t>
+  </si>
+  <si>
+    <t>Feel Good Inc.</t>
+  </si>
+  <si>
+    <t>La Flûte enchantée – Air de la Reine de la nuit</t>
+  </si>
+  <si>
+    <t>Gracias a la Vida</t>
+  </si>
+  <si>
+    <t>Manhattan-Kaboul</t>
+  </si>
+  <si>
+    <t>Can You Feel the Love Tonight</t>
+  </si>
+  <si>
+    <t>Symphonie fantastique – Marche au supplice</t>
+  </si>
+  <si>
+    <t>Wave</t>
+  </si>
+  <si>
+    <t>Petite Marie</t>
+  </si>
+  <si>
+    <t>Chandelier</t>
+  </si>
+  <si>
+    <t>Ma mère l'Oye – Pavane de la Belle au bois dormant</t>
+  </si>
+  <si>
+    <t>Águas de Março</t>
+  </si>
+  <si>
+    <t>3 nuits par semaine</t>
+  </si>
+  <si>
+    <t>The Less I Know the Better</t>
+  </si>
+  <si>
+    <t>Ave Maria</t>
+  </si>
+  <si>
+    <t>Libertine</t>
+  </si>
+  <si>
+    <t>Desert Rose</t>
+  </si>
+  <si>
+    <t>Berceuse, op. 49 n°4</t>
+  </si>
+  <si>
+    <t>Foux Du Fa Fa</t>
+  </si>
+  <si>
+    <t>Zen</t>
+  </si>
+  <si>
+    <t>Jóga</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1366,13 +1791,24 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1388,11 +1824,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1740,7 +2177,6 @@
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" customWidth="1"/>
     <col min="5" max="5" width="35.6640625" customWidth="1"/>
-    <col min="6" max="6" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2527,25 +2963,22 @@
       <c r="D46" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46359</v>
       </c>
       <c r="B47" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" t="s">
         <v>162</v>
-      </c>
-      <c r="C47" t="s">
-        <v>163</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2570,16 +3003,16 @@
         <v>46363</v>
       </c>
       <c r="B49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C49" t="s">
         <v>165</v>
-      </c>
-      <c r="C49" t="s">
-        <v>166</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -2587,16 +3020,16 @@
         <v>46364</v>
       </c>
       <c r="B50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" t="s">
         <v>168</v>
-      </c>
-      <c r="C50" t="s">
-        <v>169</v>
       </c>
       <c r="D50" t="s">
         <v>160</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
@@ -2604,16 +3037,16 @@
         <v>46366</v>
       </c>
       <c r="B51" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" t="s">
         <v>171</v>
-      </c>
-      <c r="C51" t="s">
-        <v>172</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -2638,7 +3071,7 @@
         <v>46370</v>
       </c>
       <c r="B53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
         <v>60</v>
@@ -2647,7 +3080,7 @@
         <v>61</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
@@ -2655,16 +3088,16 @@
         <v>46371</v>
       </c>
       <c r="B54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" t="s">
         <v>176</v>
-      </c>
-      <c r="C54" t="s">
-        <v>177</v>
       </c>
       <c r="D54" t="s">
         <v>160</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
@@ -2672,16 +3105,16 @@
         <v>46373</v>
       </c>
       <c r="B55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" t="s">
         <v>179</v>
-      </c>
-      <c r="C55" t="s">
-        <v>180</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -2689,16 +3122,16 @@
         <v>46374</v>
       </c>
       <c r="B56" t="s">
+        <v>181</v>
+      </c>
+      <c r="C56" t="s">
         <v>182</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>183</v>
       </c>
-      <c r="D56" t="s">
+      <c r="F56" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
@@ -2706,16 +3139,16 @@
         <v>46391</v>
       </c>
       <c r="B57" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" t="s">
         <v>186</v>
-      </c>
-      <c r="C57" t="s">
-        <v>187</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -2723,16 +3156,16 @@
         <v>46392</v>
       </c>
       <c r="B58" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" t="s">
         <v>189</v>
-      </c>
-      <c r="C58" t="s">
-        <v>190</v>
       </c>
       <c r="D58" t="s">
         <v>160</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
@@ -2740,16 +3173,16 @@
         <v>46394</v>
       </c>
       <c r="B59" t="s">
+        <v>191</v>
+      </c>
+      <c r="C59" t="s">
         <v>192</v>
-      </c>
-      <c r="C59" t="s">
-        <v>193</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -2774,16 +3207,16 @@
         <v>46398</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -2791,16 +3224,16 @@
         <v>46399</v>
       </c>
       <c r="B62" t="s">
+        <v>196</v>
+      </c>
+      <c r="C62" t="s">
         <v>197</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>198</v>
       </c>
-      <c r="D62" t="s">
+      <c r="F62" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
@@ -2808,16 +3241,16 @@
         <v>46401</v>
       </c>
       <c r="B63" t="s">
+        <v>200</v>
+      </c>
+      <c r="C63" t="s">
         <v>201</v>
-      </c>
-      <c r="C63" t="s">
-        <v>202</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
@@ -2825,16 +3258,16 @@
         <v>46402</v>
       </c>
       <c r="B64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" t="s">
         <v>204</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>205</v>
       </c>
-      <c r="D64" t="s">
+      <c r="F64" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -2842,7 +3275,7 @@
         <v>46405</v>
       </c>
       <c r="B65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C65" t="s">
         <v>46</v>
@@ -2851,7 +3284,7 @@
         <v>24</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -2859,16 +3292,16 @@
         <v>46406</v>
       </c>
       <c r="B66" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" t="s">
         <v>210</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>211</v>
       </c>
-      <c r="D66" t="s">
+      <c r="F66" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
@@ -2876,16 +3309,16 @@
         <v>46408</v>
       </c>
       <c r="B67" t="s">
+        <v>213</v>
+      </c>
+      <c r="C67" t="s">
         <v>214</v>
-      </c>
-      <c r="C67" t="s">
-        <v>215</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
@@ -2893,16 +3326,16 @@
         <v>46409</v>
       </c>
       <c r="B68" t="s">
+        <v>216</v>
+      </c>
+      <c r="C68" t="s">
         <v>217</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>218</v>
       </c>
-      <c r="D68" t="s">
+      <c r="F68" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
@@ -2910,16 +3343,16 @@
         <v>46412</v>
       </c>
       <c r="B69" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" t="s">
         <v>221</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>222</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -2927,16 +3360,16 @@
         <v>46413</v>
       </c>
       <c r="B70" t="s">
+        <v>224</v>
+      </c>
+      <c r="C70" t="s">
         <v>225</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
+        <v>211</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="D70" t="s">
-        <v>212</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -2944,16 +3377,16 @@
         <v>46415</v>
       </c>
       <c r="B71" t="s">
+        <v>227</v>
+      </c>
+      <c r="C71" t="s">
         <v>228</v>
-      </c>
-      <c r="C71" t="s">
-        <v>229</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
@@ -2961,16 +3394,16 @@
         <v>46416</v>
       </c>
       <c r="B72" t="s">
+        <v>230</v>
+      </c>
+      <c r="C72" t="s">
         <v>231</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>232</v>
       </c>
-      <c r="D72" t="s">
+      <c r="F72" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
@@ -2978,16 +3411,16 @@
         <v>46419</v>
       </c>
       <c r="B73" t="s">
+        <v>234</v>
+      </c>
+      <c r="C73" t="s">
         <v>235</v>
-      </c>
-      <c r="C73" t="s">
-        <v>236</v>
       </c>
       <c r="D73" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
@@ -2995,16 +3428,16 @@
         <v>46420</v>
       </c>
       <c r="B74" t="s">
+        <v>237</v>
+      </c>
+      <c r="C74" t="s">
         <v>238</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>239</v>
       </c>
-      <c r="D74" t="s">
+      <c r="F74" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
@@ -3012,16 +3445,16 @@
         <v>46422</v>
       </c>
       <c r="B75" t="s">
+        <v>241</v>
+      </c>
+      <c r="C75" t="s">
         <v>242</v>
-      </c>
-      <c r="C75" t="s">
-        <v>243</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3029,16 +3462,16 @@
         <v>46423</v>
       </c>
       <c r="B76" t="s">
+        <v>244</v>
+      </c>
+      <c r="C76" t="s">
         <v>245</v>
-      </c>
-      <c r="C76" t="s">
-        <v>246</v>
       </c>
       <c r="D76" t="s">
         <v>100</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -3046,16 +3479,16 @@
         <v>46426</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C77" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D77" t="s">
         <v>17</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
@@ -3063,16 +3496,16 @@
         <v>46427</v>
       </c>
       <c r="B78" t="s">
+        <v>249</v>
+      </c>
+      <c r="C78" t="s">
         <v>250</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>251</v>
       </c>
-      <c r="D78" t="s">
+      <c r="F78" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
@@ -3080,16 +3513,16 @@
         <v>46429</v>
       </c>
       <c r="B79" t="s">
+        <v>253</v>
+      </c>
+      <c r="C79" t="s">
         <v>254</v>
-      </c>
-      <c r="C79" t="s">
-        <v>255</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
@@ -3097,16 +3530,16 @@
         <v>46430</v>
       </c>
       <c r="B80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C80" t="s">
         <v>257</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>258</v>
       </c>
-      <c r="D80" t="s">
+      <c r="F80" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -3114,16 +3547,16 @@
         <v>46433</v>
       </c>
       <c r="B81" t="s">
+        <v>260</v>
+      </c>
+      <c r="C81" t="s">
         <v>261</v>
-      </c>
-      <c r="C81" t="s">
-        <v>262</v>
       </c>
       <c r="D81" t="s">
         <v>156</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
@@ -3131,16 +3564,16 @@
         <v>46434</v>
       </c>
       <c r="B82" t="s">
+        <v>263</v>
+      </c>
+      <c r="C82" t="s">
         <v>264</v>
-      </c>
-      <c r="C82" t="s">
-        <v>265</v>
       </c>
       <c r="D82" t="s">
         <v>71</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
@@ -3148,16 +3581,16 @@
         <v>46436</v>
       </c>
       <c r="B83" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" t="s">
         <v>267</v>
-      </c>
-      <c r="C83" t="s">
-        <v>268</v>
       </c>
       <c r="D83" t="s">
         <v>13</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
@@ -3165,16 +3598,16 @@
         <v>46437</v>
       </c>
       <c r="B84" t="s">
+        <v>269</v>
+      </c>
+      <c r="C84" t="s">
         <v>270</v>
-      </c>
-      <c r="C84" t="s">
-        <v>271</v>
       </c>
       <c r="D84" t="s">
         <v>50</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
@@ -3182,16 +3615,16 @@
         <v>46454</v>
       </c>
       <c r="B85" t="s">
+        <v>272</v>
+      </c>
+      <c r="C85" t="s">
         <v>273</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>274</v>
       </c>
-      <c r="D85" t="s">
+      <c r="F85" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
@@ -3216,16 +3649,16 @@
         <v>46457</v>
       </c>
       <c r="B87" t="s">
+        <v>276</v>
+      </c>
+      <c r="C87" t="s">
         <v>277</v>
-      </c>
-      <c r="C87" t="s">
-        <v>278</v>
       </c>
       <c r="D87" t="s">
         <v>13</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
@@ -3233,16 +3666,16 @@
         <v>46458</v>
       </c>
       <c r="B88" t="s">
+        <v>279</v>
+      </c>
+      <c r="C88" t="s">
         <v>280</v>
-      </c>
-      <c r="C88" t="s">
-        <v>281</v>
       </c>
       <c r="D88" t="s">
         <v>100</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
@@ -3250,16 +3683,16 @@
         <v>46461</v>
       </c>
       <c r="B89" t="s">
+        <v>282</v>
+      </c>
+      <c r="C89" t="s">
         <v>283</v>
-      </c>
-      <c r="C89" t="s">
-        <v>284</v>
       </c>
       <c r="D89" t="s">
         <v>13</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
@@ -3267,16 +3700,16 @@
         <v>46462</v>
       </c>
       <c r="B90" t="s">
+        <v>285</v>
+      </c>
+      <c r="C90" t="s">
         <v>286</v>
-      </c>
-      <c r="C90" t="s">
-        <v>287</v>
       </c>
       <c r="D90" t="s">
         <v>100</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
@@ -3284,16 +3717,16 @@
         <v>46464</v>
       </c>
       <c r="B91" t="s">
+        <v>288</v>
+      </c>
+      <c r="C91" t="s">
         <v>289</v>
-      </c>
-      <c r="C91" t="s">
-        <v>290</v>
       </c>
       <c r="D91" t="s">
         <v>13</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
@@ -3301,16 +3734,16 @@
         <v>46465</v>
       </c>
       <c r="B92" t="s">
+        <v>291</v>
+      </c>
+      <c r="C92" t="s">
         <v>292</v>
-      </c>
-      <c r="C92" t="s">
-        <v>293</v>
       </c>
       <c r="D92" t="s">
         <v>100</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
@@ -3318,16 +3751,16 @@
         <v>46468</v>
       </c>
       <c r="B93" t="s">
+        <v>294</v>
+      </c>
+      <c r="C93" t="s">
         <v>295</v>
-      </c>
-      <c r="C93" t="s">
-        <v>296</v>
       </c>
       <c r="D93" t="s">
         <v>13</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
@@ -3335,16 +3768,16 @@
         <v>46469</v>
       </c>
       <c r="B94" t="s">
+        <v>297</v>
+      </c>
+      <c r="C94" t="s">
         <v>298</v>
-      </c>
-      <c r="C94" t="s">
-        <v>299</v>
       </c>
       <c r="D94" t="s">
         <v>100</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
@@ -3352,16 +3785,16 @@
         <v>46471</v>
       </c>
       <c r="B95" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
@@ -3369,16 +3802,16 @@
         <v>46472</v>
       </c>
       <c r="B96" t="s">
+        <v>302</v>
+      </c>
+      <c r="C96" t="s">
         <v>303</v>
-      </c>
-      <c r="C96" t="s">
-        <v>304</v>
       </c>
       <c r="D96" t="s">
         <v>100</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
@@ -3386,16 +3819,16 @@
         <v>46475</v>
       </c>
       <c r="B97" t="s">
+        <v>305</v>
+      </c>
+      <c r="C97" t="s">
         <v>306</v>
-      </c>
-      <c r="C97" t="s">
-        <v>307</v>
       </c>
       <c r="D97" t="s">
         <v>13</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -3420,16 +3853,16 @@
         <v>46478</v>
       </c>
       <c r="B99" t="s">
+        <v>308</v>
+      </c>
+      <c r="C99" t="s">
         <v>309</v>
-      </c>
-      <c r="C99" t="s">
-        <v>310</v>
       </c>
       <c r="D99" t="s">
         <v>13</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
@@ -3437,16 +3870,16 @@
         <v>46479</v>
       </c>
       <c r="B100" t="s">
+        <v>311</v>
+      </c>
+      <c r="C100" t="s">
         <v>312</v>
-      </c>
-      <c r="C100" t="s">
-        <v>313</v>
       </c>
       <c r="D100" t="s">
         <v>50</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
@@ -3471,16 +3904,16 @@
         <v>46485</v>
       </c>
       <c r="B102" t="s">
+        <v>314</v>
+      </c>
+      <c r="C102" t="s">
         <v>315</v>
-      </c>
-      <c r="C102" t="s">
-        <v>316</v>
       </c>
       <c r="D102" t="s">
         <v>13</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
@@ -3488,16 +3921,16 @@
         <v>46486</v>
       </c>
       <c r="B103" t="s">
+        <v>317</v>
+      </c>
+      <c r="C103" t="s">
         <v>318</v>
-      </c>
-      <c r="C103" t="s">
-        <v>319</v>
       </c>
       <c r="D103" t="s">
         <v>50</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
@@ -3505,16 +3938,16 @@
         <v>46489</v>
       </c>
       <c r="B104" t="s">
+        <v>320</v>
+      </c>
+      <c r="C104" t="s">
         <v>321</v>
-      </c>
-      <c r="C104" t="s">
-        <v>322</v>
       </c>
       <c r="D104" t="s">
         <v>100</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
@@ -3522,16 +3955,16 @@
         <v>46490</v>
       </c>
       <c r="B105" t="s">
+        <v>323</v>
+      </c>
+      <c r="C105" t="s">
         <v>324</v>
-      </c>
-      <c r="C105" t="s">
-        <v>325</v>
       </c>
       <c r="D105" t="s">
         <v>100</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
@@ -3539,16 +3972,16 @@
         <v>46492</v>
       </c>
       <c r="B106" t="s">
+        <v>326</v>
+      </c>
+      <c r="C106" t="s">
         <v>327</v>
-      </c>
-      <c r="C106" t="s">
-        <v>328</v>
       </c>
       <c r="D106" t="s">
         <v>13</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
@@ -3556,16 +3989,16 @@
         <v>46493</v>
       </c>
       <c r="B107" t="s">
+        <v>329</v>
+      </c>
+      <c r="C107" t="s">
         <v>330</v>
-      </c>
-      <c r="C107" t="s">
-        <v>331</v>
       </c>
       <c r="D107" t="s">
         <v>50</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
@@ -3573,16 +4006,16 @@
         <v>46496</v>
       </c>
       <c r="B108" t="s">
+        <v>332</v>
+      </c>
+      <c r="C108" t="s">
         <v>333</v>
-      </c>
-      <c r="C108" t="s">
-        <v>334</v>
       </c>
       <c r="D108" t="s">
         <v>13</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
@@ -3607,16 +4040,16 @@
         <v>46499</v>
       </c>
       <c r="B110" t="s">
+        <v>335</v>
+      </c>
+      <c r="C110" t="s">
         <v>336</v>
-      </c>
-      <c r="C110" t="s">
-        <v>337</v>
       </c>
       <c r="D110" t="s">
         <v>13</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
@@ -3624,16 +4057,16 @@
         <v>46500</v>
       </c>
       <c r="B111" t="s">
+        <v>338</v>
+      </c>
+      <c r="C111" t="s">
         <v>339</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>340</v>
       </c>
-      <c r="D111" t="s">
+      <c r="F111" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
@@ -3641,16 +4074,16 @@
         <v>46510</v>
       </c>
       <c r="B112" t="s">
+        <v>342</v>
+      </c>
+      <c r="C112" t="s">
         <v>343</v>
-      </c>
-      <c r="C112" t="s">
-        <v>344</v>
       </c>
       <c r="D112" t="s">
         <v>50</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
@@ -3658,16 +4091,16 @@
         <v>46511</v>
       </c>
       <c r="B113" t="s">
+        <v>345</v>
+      </c>
+      <c r="C113" t="s">
         <v>346</v>
-      </c>
-      <c r="C113" t="s">
-        <v>347</v>
       </c>
       <c r="D113" t="s">
         <v>100</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
@@ -3675,7 +4108,7 @@
         <v>46517</v>
       </c>
       <c r="B114" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C114" t="s">
         <v>129</v>
@@ -3684,7 +4117,7 @@
         <v>17</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
@@ -3692,16 +4125,16 @@
         <v>46518</v>
       </c>
       <c r="B115" t="s">
+        <v>350</v>
+      </c>
+      <c r="C115" t="s">
         <v>351</v>
-      </c>
-      <c r="C115" t="s">
-        <v>352</v>
       </c>
       <c r="D115" t="s">
         <v>100</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
@@ -3709,16 +4142,16 @@
         <v>46520</v>
       </c>
       <c r="B116" t="s">
+        <v>353</v>
+      </c>
+      <c r="C116" t="s">
         <v>354</v>
-      </c>
-      <c r="C116" t="s">
-        <v>355</v>
       </c>
       <c r="D116" t="s">
         <v>13</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
@@ -3726,16 +4159,16 @@
         <v>46521</v>
       </c>
       <c r="B117" t="s">
+        <v>356</v>
+      </c>
+      <c r="C117" t="s">
         <v>357</v>
-      </c>
-      <c r="C117" t="s">
-        <v>358</v>
       </c>
       <c r="D117" t="s">
         <v>100</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
@@ -3743,16 +4176,16 @@
         <v>46525</v>
       </c>
       <c r="B118" t="s">
+        <v>359</v>
+      </c>
+      <c r="C118" t="s">
         <v>360</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>361</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
@@ -3760,16 +4193,16 @@
         <v>46527</v>
       </c>
       <c r="B119" t="s">
+        <v>363</v>
+      </c>
+      <c r="C119" t="s">
         <v>364</v>
-      </c>
-      <c r="C119" t="s">
-        <v>365</v>
       </c>
       <c r="D119" t="s">
         <v>13</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
@@ -3777,16 +4210,16 @@
         <v>46528</v>
       </c>
       <c r="B120" t="s">
+        <v>366</v>
+      </c>
+      <c r="C120" t="s">
         <v>367</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>361</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="D120" t="s">
-        <v>362</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
@@ -3794,16 +4227,16 @@
         <v>46531</v>
       </c>
       <c r="B121" t="s">
+        <v>369</v>
+      </c>
+      <c r="C121" t="s">
         <v>370</v>
-      </c>
-      <c r="C121" t="s">
-        <v>371</v>
       </c>
       <c r="D121" t="s">
         <v>17</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
@@ -3811,16 +4244,16 @@
         <v>46532</v>
       </c>
       <c r="B122" t="s">
+        <v>372</v>
+      </c>
+      <c r="C122" t="s">
         <v>373</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>374</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
@@ -3828,16 +4261,16 @@
         <v>46534</v>
       </c>
       <c r="B123" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" t="s">
         <v>377</v>
-      </c>
-      <c r="C123" t="s">
-        <v>378</v>
       </c>
       <c r="D123" t="s">
         <v>13</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
@@ -3845,16 +4278,16 @@
         <v>46535</v>
       </c>
       <c r="B124" t="s">
+        <v>379</v>
+      </c>
+      <c r="C124" t="s">
         <v>380</v>
-      </c>
-      <c r="C124" t="s">
-        <v>381</v>
       </c>
       <c r="D124" t="s">
         <v>50</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
@@ -3862,7 +4295,7 @@
         <v>46538</v>
       </c>
       <c r="B125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
         <v>60</v>
@@ -3871,7 +4304,7 @@
         <v>61</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
@@ -3879,16 +4312,16 @@
         <v>46539</v>
       </c>
       <c r="B126" t="s">
+        <v>384</v>
+      </c>
+      <c r="C126" t="s">
         <v>385</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
+        <v>374</v>
+      </c>
+      <c r="F126" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="D126" t="s">
-        <v>375</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
@@ -3896,16 +4329,16 @@
         <v>46541</v>
       </c>
       <c r="B127" t="s">
+        <v>387</v>
+      </c>
+      <c r="C127" t="s">
         <v>388</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
         <v>389</v>
       </c>
-      <c r="D127" t="s">
+      <c r="F127" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
@@ -3913,16 +4346,16 @@
         <v>46542</v>
       </c>
       <c r="B128" t="s">
+        <v>391</v>
+      </c>
+      <c r="C128" t="s">
         <v>392</v>
-      </c>
-      <c r="C128" t="s">
-        <v>393</v>
       </c>
       <c r="D128" t="s">
         <v>50</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
@@ -3930,16 +4363,16 @@
         <v>46545</v>
       </c>
       <c r="B129" t="s">
+        <v>394</v>
+      </c>
+      <c r="C129" t="s">
         <v>395</v>
-      </c>
-      <c r="C129" t="s">
-        <v>396</v>
       </c>
       <c r="D129" t="s">
         <v>13</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
@@ -3947,16 +4380,16 @@
         <v>46546</v>
       </c>
       <c r="B130" t="s">
+        <v>397</v>
+      </c>
+      <c r="C130" t="s">
         <v>398</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
+        <v>218</v>
+      </c>
+      <c r="F130" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="D130" t="s">
-        <v>219</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
@@ -3964,7 +4397,7 @@
         <v>46548</v>
       </c>
       <c r="B131" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C131" t="s">
         <v>110</v>
@@ -3973,7 +4406,7 @@
         <v>13</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
@@ -3981,16 +4414,16 @@
         <v>46549</v>
       </c>
       <c r="B132" t="s">
+        <v>402</v>
+      </c>
+      <c r="C132" t="s">
         <v>403</v>
-      </c>
-      <c r="C132" t="s">
-        <v>404</v>
       </c>
       <c r="D132" t="s">
         <v>31</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
@@ -3998,16 +4431,16 @@
         <v>46552</v>
       </c>
       <c r="B133" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C133" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D133" t="s">
         <v>13</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
@@ -4015,16 +4448,16 @@
         <v>46553</v>
       </c>
       <c r="B134" t="s">
+        <v>407</v>
+      </c>
+      <c r="C134" t="s">
         <v>408</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
+        <v>218</v>
+      </c>
+      <c r="F134" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="D134" t="s">
-        <v>219</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
@@ -4032,16 +4465,16 @@
         <v>46555</v>
       </c>
       <c r="B135" t="s">
+        <v>410</v>
+      </c>
+      <c r="C135" t="s">
         <v>411</v>
-      </c>
-      <c r="C135" t="s">
-        <v>412</v>
       </c>
       <c r="D135" t="s">
         <v>13</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
@@ -4049,16 +4482,16 @@
         <v>46556</v>
       </c>
       <c r="B136" t="s">
+        <v>413</v>
+      </c>
+      <c r="C136" t="s">
         <v>414</v>
-      </c>
-      <c r="C136" t="s">
-        <v>415</v>
       </c>
       <c r="D136" t="s">
         <v>31</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
@@ -4066,7 +4499,7 @@
         <v>46559</v>
       </c>
       <c r="B137" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C137" t="s">
         <v>116</v>
@@ -4075,7 +4508,7 @@
         <v>61</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
@@ -4100,16 +4533,16 @@
         <v>46562</v>
       </c>
       <c r="B139" t="s">
+        <v>418</v>
+      </c>
+      <c r="C139" t="s">
         <v>419</v>
-      </c>
-      <c r="C139" t="s">
-        <v>420</v>
       </c>
       <c r="D139" t="s">
         <v>13</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
@@ -4117,16 +4550,16 @@
         <v>46563</v>
       </c>
       <c r="B140" t="s">
+        <v>421</v>
+      </c>
+      <c r="C140" t="s">
         <v>422</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>423</v>
       </c>
-      <c r="D140" t="s">
+      <c r="F140" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
@@ -4134,16 +4567,16 @@
         <v>46566</v>
       </c>
       <c r="B141" t="s">
+        <v>425</v>
+      </c>
+      <c r="C141" t="s">
         <v>426</v>
-      </c>
-      <c r="C141" t="s">
-        <v>427</v>
       </c>
       <c r="D141" t="s">
         <v>17</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
@@ -4151,16 +4584,16 @@
         <v>46567</v>
       </c>
       <c r="B142" t="s">
+        <v>428</v>
+      </c>
+      <c r="C142" t="s">
         <v>429</v>
-      </c>
-      <c r="C142" t="s">
-        <v>430</v>
       </c>
       <c r="D142" t="s">
         <v>86</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
@@ -4168,16 +4601,16 @@
         <v>46569</v>
       </c>
       <c r="B143" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C143" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D143" t="s">
         <v>13</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
@@ -4185,16 +4618,16 @@
         <v>46570</v>
       </c>
       <c r="B144" t="s">
+        <v>433</v>
+      </c>
+      <c r="C144" t="s">
         <v>434</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>435</v>
       </c>
-      <c r="D144" t="s">
+      <c r="F144" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -4248,106 +4681,2567 @@
     <hyperlink ref="F43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
     <hyperlink ref="F44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
     <hyperlink ref="F45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="F47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="F49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="F51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="F53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="F57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="F58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="F62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="F63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="F65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="F66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="F67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="F71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="F73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="F75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="F77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="F82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="F90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="F91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="F92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="F94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="F95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="F96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="F97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="F98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="F99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="F100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="F101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="F102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="F103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="F104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="F105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="F106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="F107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="F108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="F109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="F110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="F111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="F112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="F113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="F114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="F115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="F116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="F117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="F118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="F119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="F120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="F121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="F122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="F123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="F124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="F125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="F126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="F127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="F128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="F129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="F130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="F131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="F132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="F133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="F134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="F135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="F136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="F137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="F138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F139" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="F140" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="F141" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="F142" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="F143" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F144" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="F47" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F48" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F49" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F50" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F51" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F52" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F53" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F54" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="F55" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F56" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F57" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F58" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="F59" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="F64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="F66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F74" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F75" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F76" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F77" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F79" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F80" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F82" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F83" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="F88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="F91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="F92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="F93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="F95" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="F96" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="F98" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F99" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F100" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F101" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F102" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F103" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="F104" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F105" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="F106" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="F107" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="F108" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F109" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="F110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="F112" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F113" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="F114" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F115" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="F116" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F117" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="F118" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F119" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="F120" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F121" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="F122" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="F123" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="F124" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="F125" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="F126" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="F127" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="F128" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="F129" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="F130" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="F131" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="F132" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="F133" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="F134" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="F135" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="F136" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="F137" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="F138" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F139" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="F140" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="F141" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="F142" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="F143" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="F144" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E144"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>452</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>454</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>455</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>456</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>458</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>459</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>460</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>461</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>462</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>463</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>465</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>466</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>467</v>
+      </c>
+      <c r="C25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>468</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>469</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>470</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>471</v>
+      </c>
+      <c r="C29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>472</v>
+      </c>
+      <c r="C30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>473</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>474</v>
+      </c>
+      <c r="C32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>475</v>
+      </c>
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>476</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>478</v>
+      </c>
+      <c r="C36" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>479</v>
+      </c>
+      <c r="C37" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>480</v>
+      </c>
+      <c r="C38" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>481</v>
+      </c>
+      <c r="C39" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>482</v>
+      </c>
+      <c r="C40" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>483</v>
+      </c>
+      <c r="C41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>484</v>
+      </c>
+      <c r="C42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D42" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>485</v>
+      </c>
+      <c r="C43" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>486</v>
+      </c>
+      <c r="C44" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" t="s">
+        <v>153</v>
+      </c>
+      <c r="E44" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>487</v>
+      </c>
+      <c r="C45" t="s">
+        <v>155</v>
+      </c>
+      <c r="D45" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>488</v>
+      </c>
+      <c r="C46" t="s">
+        <v>159</v>
+      </c>
+      <c r="E46" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>489</v>
+      </c>
+      <c r="C47" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>464</v>
+      </c>
+      <c r="C48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>490</v>
+      </c>
+      <c r="C49" t="s">
+        <v>165</v>
+      </c>
+      <c r="D49" t="s">
+        <v>166</v>
+      </c>
+      <c r="E49" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>491</v>
+      </c>
+      <c r="C50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
+        <v>492</v>
+      </c>
+      <c r="C51" t="s">
+        <v>171</v>
+      </c>
+      <c r="D51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s">
+        <v>476</v>
+      </c>
+      <c r="C52" t="s">
+        <v>119</v>
+      </c>
+      <c r="D52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>493</v>
+      </c>
+      <c r="C53" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" t="s">
+        <v>174</v>
+      </c>
+      <c r="E53" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54" t="s">
+        <v>494</v>
+      </c>
+      <c r="C54" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>495</v>
+      </c>
+      <c r="C55" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" t="s">
+        <v>180</v>
+      </c>
+      <c r="E55" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>496</v>
+      </c>
+      <c r="C56" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>497</v>
+      </c>
+      <c r="C57" t="s">
+        <v>186</v>
+      </c>
+      <c r="D57" t="s">
+        <v>187</v>
+      </c>
+      <c r="E57" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>498</v>
+      </c>
+      <c r="C58" t="s">
+        <v>189</v>
+      </c>
+      <c r="D58" t="s">
+        <v>190</v>
+      </c>
+      <c r="E58" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C59" t="s">
+        <v>192</v>
+      </c>
+      <c r="D59" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60" t="s">
+        <v>480</v>
+      </c>
+      <c r="C60" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" t="s">
+        <v>134</v>
+      </c>
+      <c r="E60" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>500</v>
+      </c>
+      <c r="C61" t="s">
+        <v>186</v>
+      </c>
+      <c r="D61" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>501</v>
+      </c>
+      <c r="C62" t="s">
+        <v>197</v>
+      </c>
+      <c r="D62" t="s">
+        <v>199</v>
+      </c>
+      <c r="E62" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>63</v>
+      </c>
+      <c r="B63" t="s">
+        <v>502</v>
+      </c>
+      <c r="C63" t="s">
+        <v>201</v>
+      </c>
+      <c r="D63" t="s">
+        <v>202</v>
+      </c>
+      <c r="E63" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>503</v>
+      </c>
+      <c r="C64" t="s">
+        <v>204</v>
+      </c>
+      <c r="D64" t="s">
+        <v>206</v>
+      </c>
+      <c r="E64" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65" t="s">
+        <v>504</v>
+      </c>
+      <c r="C65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>505</v>
+      </c>
+      <c r="C66" t="s">
+        <v>210</v>
+      </c>
+      <c r="D66" t="s">
+        <v>212</v>
+      </c>
+      <c r="E66" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>67</v>
+      </c>
+      <c r="B67" t="s">
+        <v>506</v>
+      </c>
+      <c r="C67" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" t="s">
+        <v>215</v>
+      </c>
+      <c r="E67" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>68</v>
+      </c>
+      <c r="B68" t="s">
+        <v>507</v>
+      </c>
+      <c r="C68" t="s">
+        <v>217</v>
+      </c>
+      <c r="D68" t="s">
+        <v>219</v>
+      </c>
+      <c r="E68" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>69</v>
+      </c>
+      <c r="B69" t="s">
+        <v>508</v>
+      </c>
+      <c r="C69" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" t="s">
+        <v>223</v>
+      </c>
+      <c r="E69" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>509</v>
+      </c>
+      <c r="C70" t="s">
+        <v>225</v>
+      </c>
+      <c r="D70" t="s">
+        <v>226</v>
+      </c>
+      <c r="E70" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>71</v>
+      </c>
+      <c r="B71" t="s">
+        <v>510</v>
+      </c>
+      <c r="C71" t="s">
+        <v>228</v>
+      </c>
+      <c r="D71" t="s">
+        <v>229</v>
+      </c>
+      <c r="E71" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>72</v>
+      </c>
+      <c r="B72" t="s">
+        <v>511</v>
+      </c>
+      <c r="C72" t="s">
+        <v>231</v>
+      </c>
+      <c r="D72" t="s">
+        <v>233</v>
+      </c>
+      <c r="E72" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>73</v>
+      </c>
+      <c r="B73" t="s">
+        <v>512</v>
+      </c>
+      <c r="C73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D73" t="s">
+        <v>236</v>
+      </c>
+      <c r="E73" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>74</v>
+      </c>
+      <c r="B74" t="s">
+        <v>513</v>
+      </c>
+      <c r="C74" t="s">
+        <v>238</v>
+      </c>
+      <c r="D74" t="s">
+        <v>240</v>
+      </c>
+      <c r="E74" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>75</v>
+      </c>
+      <c r="B75" t="s">
+        <v>514</v>
+      </c>
+      <c r="C75" t="s">
+        <v>242</v>
+      </c>
+      <c r="D75" t="s">
+        <v>243</v>
+      </c>
+      <c r="E75" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>76</v>
+      </c>
+      <c r="B76" t="s">
+        <v>515</v>
+      </c>
+      <c r="C76" t="s">
+        <v>245</v>
+      </c>
+      <c r="D76" t="s">
+        <v>246</v>
+      </c>
+      <c r="E76" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>77</v>
+      </c>
+      <c r="B77" t="s">
+        <v>516</v>
+      </c>
+      <c r="C77" t="s">
+        <v>235</v>
+      </c>
+      <c r="D77" t="s">
+        <v>248</v>
+      </c>
+      <c r="E77" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>78</v>
+      </c>
+      <c r="B78" t="s">
+        <v>517</v>
+      </c>
+      <c r="C78" t="s">
+        <v>250</v>
+      </c>
+      <c r="D78" t="s">
+        <v>252</v>
+      </c>
+      <c r="E78" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>79</v>
+      </c>
+      <c r="B79" t="s">
+        <v>518</v>
+      </c>
+      <c r="C79" t="s">
+        <v>254</v>
+      </c>
+      <c r="D79" t="s">
+        <v>255</v>
+      </c>
+      <c r="E79" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>80</v>
+      </c>
+      <c r="B80" t="s">
+        <v>519</v>
+      </c>
+      <c r="C80" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80" t="s">
+        <v>259</v>
+      </c>
+      <c r="E80" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>81</v>
+      </c>
+      <c r="B81" t="s">
+        <v>520</v>
+      </c>
+      <c r="C81" t="s">
+        <v>261</v>
+      </c>
+      <c r="D81" t="s">
+        <v>262</v>
+      </c>
+      <c r="E81" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>521</v>
+      </c>
+      <c r="C82" t="s">
+        <v>264</v>
+      </c>
+      <c r="D82" t="s">
+        <v>265</v>
+      </c>
+      <c r="E82" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>83</v>
+      </c>
+      <c r="B83" t="s">
+        <v>522</v>
+      </c>
+      <c r="C83" t="s">
+        <v>267</v>
+      </c>
+      <c r="D83" t="s">
+        <v>268</v>
+      </c>
+      <c r="E83" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>84</v>
+      </c>
+      <c r="B84" t="s">
+        <v>523</v>
+      </c>
+      <c r="C84" t="s">
+        <v>270</v>
+      </c>
+      <c r="D84" t="s">
+        <v>271</v>
+      </c>
+      <c r="E84" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>85</v>
+      </c>
+      <c r="B85" t="s">
+        <v>524</v>
+      </c>
+      <c r="C85" t="s">
+        <v>273</v>
+      </c>
+      <c r="D85" t="s">
+        <v>275</v>
+      </c>
+      <c r="E85" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="B86" t="s">
+        <v>474</v>
+      </c>
+      <c r="C86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E86" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>525</v>
+      </c>
+      <c r="C87" t="s">
+        <v>277</v>
+      </c>
+      <c r="D87" t="s">
+        <v>278</v>
+      </c>
+      <c r="E87" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>526</v>
+      </c>
+      <c r="C88" t="s">
+        <v>280</v>
+      </c>
+      <c r="D88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E88" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
+        <v>527</v>
+      </c>
+      <c r="C89" t="s">
+        <v>283</v>
+      </c>
+      <c r="D89" t="s">
+        <v>284</v>
+      </c>
+      <c r="E89" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>90</v>
+      </c>
+      <c r="B90" t="s">
+        <v>528</v>
+      </c>
+      <c r="C90" t="s">
+        <v>286</v>
+      </c>
+      <c r="D90" t="s">
+        <v>287</v>
+      </c>
+      <c r="E90" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>529</v>
+      </c>
+      <c r="C91" t="s">
+        <v>289</v>
+      </c>
+      <c r="D91" t="s">
+        <v>290</v>
+      </c>
+      <c r="E91" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>530</v>
+      </c>
+      <c r="C92" t="s">
+        <v>292</v>
+      </c>
+      <c r="D92" t="s">
+        <v>293</v>
+      </c>
+      <c r="E92" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>93</v>
+      </c>
+      <c r="B93" t="s">
+        <v>531</v>
+      </c>
+      <c r="C93" t="s">
+        <v>295</v>
+      </c>
+      <c r="D93" t="s">
+        <v>296</v>
+      </c>
+      <c r="E93" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>532</v>
+      </c>
+      <c r="C94" t="s">
+        <v>298</v>
+      </c>
+      <c r="D94" t="s">
+        <v>299</v>
+      </c>
+      <c r="E94" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>533</v>
+      </c>
+      <c r="C95" t="s">
+        <v>214</v>
+      </c>
+      <c r="D95" t="s">
+        <v>301</v>
+      </c>
+      <c r="E95" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>96</v>
+      </c>
+      <c r="B96" t="s">
+        <v>534</v>
+      </c>
+      <c r="C96" t="s">
+        <v>303</v>
+      </c>
+      <c r="D96" t="s">
+        <v>304</v>
+      </c>
+      <c r="E96" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>97</v>
+      </c>
+      <c r="B97" t="s">
+        <v>535</v>
+      </c>
+      <c r="C97" t="s">
+        <v>306</v>
+      </c>
+      <c r="D97" t="s">
+        <v>307</v>
+      </c>
+      <c r="E97" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>482</v>
+      </c>
+      <c r="C98" t="s">
+        <v>139</v>
+      </c>
+      <c r="D98" t="s">
+        <v>140</v>
+      </c>
+      <c r="E98" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>536</v>
+      </c>
+      <c r="C99" t="s">
+        <v>309</v>
+      </c>
+      <c r="D99" t="s">
+        <v>310</v>
+      </c>
+      <c r="E99" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100" t="s">
+        <v>537</v>
+      </c>
+      <c r="C100" t="s">
+        <v>312</v>
+      </c>
+      <c r="D100" t="s">
+        <v>313</v>
+      </c>
+      <c r="E100" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>101</v>
+      </c>
+      <c r="B101" t="s">
+        <v>486</v>
+      </c>
+      <c r="C101" t="s">
+        <v>152</v>
+      </c>
+      <c r="D101" t="s">
+        <v>153</v>
+      </c>
+      <c r="E101" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>102</v>
+      </c>
+      <c r="B102" t="s">
+        <v>538</v>
+      </c>
+      <c r="C102" t="s">
+        <v>315</v>
+      </c>
+      <c r="D102" t="s">
+        <v>316</v>
+      </c>
+      <c r="E102" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>103</v>
+      </c>
+      <c r="B103" t="s">
+        <v>539</v>
+      </c>
+      <c r="C103" t="s">
+        <v>318</v>
+      </c>
+      <c r="D103" t="s">
+        <v>319</v>
+      </c>
+      <c r="E103" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>104</v>
+      </c>
+      <c r="B104" t="s">
+        <v>540</v>
+      </c>
+      <c r="C104" t="s">
+        <v>321</v>
+      </c>
+      <c r="D104" t="s">
+        <v>322</v>
+      </c>
+      <c r="E104" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>105</v>
+      </c>
+      <c r="B105" t="s">
+        <v>541</v>
+      </c>
+      <c r="C105" t="s">
+        <v>324</v>
+      </c>
+      <c r="D105" t="s">
+        <v>325</v>
+      </c>
+      <c r="E105" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>106</v>
+      </c>
+      <c r="B106" t="s">
+        <v>542</v>
+      </c>
+      <c r="C106" t="s">
+        <v>327</v>
+      </c>
+      <c r="D106" t="s">
+        <v>328</v>
+      </c>
+      <c r="E106" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>107</v>
+      </c>
+      <c r="B107" t="s">
+        <v>543</v>
+      </c>
+      <c r="C107" t="s">
+        <v>330</v>
+      </c>
+      <c r="D107" t="s">
+        <v>331</v>
+      </c>
+      <c r="E107" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>108</v>
+      </c>
+      <c r="B108" t="s">
+        <v>544</v>
+      </c>
+      <c r="C108" t="s">
+        <v>333</v>
+      </c>
+      <c r="D108" t="s">
+        <v>334</v>
+      </c>
+      <c r="E108" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>109</v>
+      </c>
+      <c r="B109" t="s">
+        <v>478</v>
+      </c>
+      <c r="C109" t="s">
+        <v>126</v>
+      </c>
+      <c r="D109" t="s">
+        <v>127</v>
+      </c>
+      <c r="E109" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>110</v>
+      </c>
+      <c r="B110" t="s">
+        <v>545</v>
+      </c>
+      <c r="C110" t="s">
+        <v>336</v>
+      </c>
+      <c r="D110" t="s">
+        <v>337</v>
+      </c>
+      <c r="E110" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>111</v>
+      </c>
+      <c r="B111" t="s">
+        <v>546</v>
+      </c>
+      <c r="C111" t="s">
+        <v>339</v>
+      </c>
+      <c r="D111" t="s">
+        <v>341</v>
+      </c>
+      <c r="E111" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>112</v>
+      </c>
+      <c r="B112" t="s">
+        <v>547</v>
+      </c>
+      <c r="C112" t="s">
+        <v>343</v>
+      </c>
+      <c r="D112" t="s">
+        <v>344</v>
+      </c>
+      <c r="E112" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>113</v>
+      </c>
+      <c r="B113" t="s">
+        <v>548</v>
+      </c>
+      <c r="C113" t="s">
+        <v>346</v>
+      </c>
+      <c r="D113" t="s">
+        <v>347</v>
+      </c>
+      <c r="E113" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
+        <v>549</v>
+      </c>
+      <c r="C114" t="s">
+        <v>129</v>
+      </c>
+      <c r="D114" t="s">
+        <v>349</v>
+      </c>
+      <c r="E114" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>115</v>
+      </c>
+      <c r="B115" t="s">
+        <v>550</v>
+      </c>
+      <c r="C115" t="s">
+        <v>351</v>
+      </c>
+      <c r="D115" t="s">
+        <v>352</v>
+      </c>
+      <c r="E115" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>116</v>
+      </c>
+      <c r="B116" t="s">
+        <v>551</v>
+      </c>
+      <c r="C116" t="s">
+        <v>354</v>
+      </c>
+      <c r="D116" t="s">
+        <v>355</v>
+      </c>
+      <c r="E116" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>117</v>
+      </c>
+      <c r="B117" t="s">
+        <v>552</v>
+      </c>
+      <c r="C117" t="s">
+        <v>357</v>
+      </c>
+      <c r="D117" t="s">
+        <v>358</v>
+      </c>
+      <c r="E117" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>118</v>
+      </c>
+      <c r="B118" t="s">
+        <v>553</v>
+      </c>
+      <c r="C118" t="s">
+        <v>360</v>
+      </c>
+      <c r="D118" t="s">
+        <v>362</v>
+      </c>
+      <c r="E118" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>119</v>
+      </c>
+      <c r="B119" t="s">
+        <v>554</v>
+      </c>
+      <c r="C119" t="s">
+        <v>364</v>
+      </c>
+      <c r="D119" t="s">
+        <v>365</v>
+      </c>
+      <c r="E119" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>120</v>
+      </c>
+      <c r="B120" t="s">
+        <v>555</v>
+      </c>
+      <c r="C120" t="s">
+        <v>367</v>
+      </c>
+      <c r="D120" t="s">
+        <v>368</v>
+      </c>
+      <c r="E120" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>121</v>
+      </c>
+      <c r="B121" t="s">
+        <v>556</v>
+      </c>
+      <c r="C121" t="s">
+        <v>370</v>
+      </c>
+      <c r="D121" t="s">
+        <v>371</v>
+      </c>
+      <c r="E121" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>122</v>
+      </c>
+      <c r="B122" t="s">
+        <v>557</v>
+      </c>
+      <c r="C122" t="s">
+        <v>373</v>
+      </c>
+      <c r="D122" t="s">
+        <v>375</v>
+      </c>
+      <c r="E122" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>123</v>
+      </c>
+      <c r="B123" t="s">
+        <v>558</v>
+      </c>
+      <c r="C123" t="s">
+        <v>377</v>
+      </c>
+      <c r="D123" t="s">
+        <v>378</v>
+      </c>
+      <c r="E123" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>124</v>
+      </c>
+      <c r="B124" t="s">
+        <v>559</v>
+      </c>
+      <c r="C124" t="s">
+        <v>380</v>
+      </c>
+      <c r="D124" t="s">
+        <v>381</v>
+      </c>
+      <c r="E124" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>125</v>
+      </c>
+      <c r="B125" t="s">
+        <v>560</v>
+      </c>
+      <c r="C125" t="s">
+        <v>60</v>
+      </c>
+      <c r="D125" t="s">
+        <v>383</v>
+      </c>
+      <c r="E125" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>126</v>
+      </c>
+      <c r="B126" t="s">
+        <v>561</v>
+      </c>
+      <c r="C126" t="s">
+        <v>385</v>
+      </c>
+      <c r="D126" t="s">
+        <v>386</v>
+      </c>
+      <c r="E126" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>127</v>
+      </c>
+      <c r="B127" t="s">
+        <v>562</v>
+      </c>
+      <c r="C127" t="s">
+        <v>388</v>
+      </c>
+      <c r="D127" t="s">
+        <v>390</v>
+      </c>
+      <c r="E127" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>128</v>
+      </c>
+      <c r="B128" t="s">
+        <v>563</v>
+      </c>
+      <c r="C128" t="s">
+        <v>392</v>
+      </c>
+      <c r="D128" t="s">
+        <v>393</v>
+      </c>
+      <c r="E128" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>129</v>
+      </c>
+      <c r="B129" t="s">
+        <v>564</v>
+      </c>
+      <c r="C129" t="s">
+        <v>395</v>
+      </c>
+      <c r="D129" t="s">
+        <v>396</v>
+      </c>
+      <c r="E129" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>130</v>
+      </c>
+      <c r="B130" t="s">
+        <v>565</v>
+      </c>
+      <c r="C130" t="s">
+        <v>398</v>
+      </c>
+      <c r="D130" t="s">
+        <v>399</v>
+      </c>
+      <c r="E130" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>131</v>
+      </c>
+      <c r="B131" t="s">
+        <v>566</v>
+      </c>
+      <c r="C131" t="s">
+        <v>110</v>
+      </c>
+      <c r="D131" t="s">
+        <v>401</v>
+      </c>
+      <c r="E131" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>132</v>
+      </c>
+      <c r="B132" t="s">
+        <v>567</v>
+      </c>
+      <c r="C132" t="s">
+        <v>403</v>
+      </c>
+      <c r="D132" t="s">
+        <v>404</v>
+      </c>
+      <c r="E132" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>568</v>
+      </c>
+      <c r="C133" t="s">
+        <v>306</v>
+      </c>
+      <c r="D133" t="s">
+        <v>406</v>
+      </c>
+      <c r="E133" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>134</v>
+      </c>
+      <c r="B134" t="s">
+        <v>569</v>
+      </c>
+      <c r="C134" t="s">
+        <v>408</v>
+      </c>
+      <c r="D134" t="s">
+        <v>409</v>
+      </c>
+      <c r="E134" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>135</v>
+      </c>
+      <c r="B135" t="s">
+        <v>570</v>
+      </c>
+      <c r="C135" t="s">
+        <v>411</v>
+      </c>
+      <c r="D135" t="s">
+        <v>412</v>
+      </c>
+      <c r="E135" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
+        <v>571</v>
+      </c>
+      <c r="C136" t="s">
+        <v>414</v>
+      </c>
+      <c r="D136" t="s">
+        <v>415</v>
+      </c>
+      <c r="E136" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>137</v>
+      </c>
+      <c r="B137" t="s">
+        <v>572</v>
+      </c>
+      <c r="C137" t="s">
+        <v>116</v>
+      </c>
+      <c r="D137" t="s">
+        <v>417</v>
+      </c>
+      <c r="E137" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>138</v>
+      </c>
+      <c r="B138" t="s">
+        <v>466</v>
+      </c>
+      <c r="C138" t="s">
+        <v>85</v>
+      </c>
+      <c r="D138" t="s">
+        <v>87</v>
+      </c>
+      <c r="E138" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>139</v>
+      </c>
+      <c r="B139" t="s">
+        <v>573</v>
+      </c>
+      <c r="C139" t="s">
+        <v>419</v>
+      </c>
+      <c r="D139" t="s">
+        <v>420</v>
+      </c>
+      <c r="E139" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>140</v>
+      </c>
+      <c r="B140" t="s">
+        <v>574</v>
+      </c>
+      <c r="C140" t="s">
+        <v>422</v>
+      </c>
+      <c r="D140" t="s">
+        <v>424</v>
+      </c>
+      <c r="E140" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>141</v>
+      </c>
+      <c r="B141" t="s">
+        <v>575</v>
+      </c>
+      <c r="C141" t="s">
+        <v>426</v>
+      </c>
+      <c r="D141" t="s">
+        <v>427</v>
+      </c>
+      <c r="E141" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>142</v>
+      </c>
+      <c r="B142" t="s">
+        <v>576</v>
+      </c>
+      <c r="C142" t="s">
+        <v>429</v>
+      </c>
+      <c r="D142" t="s">
+        <v>430</v>
+      </c>
+      <c r="E142" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>143</v>
+      </c>
+      <c r="B143" t="s">
+        <v>577</v>
+      </c>
+      <c r="C143" t="s">
+        <v>192</v>
+      </c>
+      <c r="D143" t="s">
+        <v>432</v>
+      </c>
+      <c r="E143" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>144</v>
+      </c>
+      <c r="B144" t="s">
+        <v>578</v>
+      </c>
+      <c r="C144" t="s">
+        <v>434</v>
+      </c>
+      <c r="D144" t="s">
+        <v>436</v>
+      </c>
+      <c r="E144" t="s">
+        <v>445</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E144" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/musique.xlsx
+++ b/musique.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Documents/Codex/2026-08-10/referenced-chatgpt-conversation-this-is-an/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B0B5391-7751-464B-9E2A-6CEABBF1B8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F06DFB9-CC40-D347-8C32-F9A48E481809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="580">
   <si>
     <t>date</t>
   </si>
@@ -1762,6 +1762,9 @@
   </si>
   <si>
     <t>Jóga</t>
+  </si>
+  <si>
+    <t>Hervé Le Sourd</t>
   </si>
 </sst>
 </file>
@@ -3516,7 +3519,7 @@
         <v>253</v>
       </c>
       <c r="C79" t="s">
-        <v>254</v>
+        <v>579</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5A4C448-6424-DA4E-AE51-78478F511CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DFA5D8-4BE0-F94F-9EA4-ADAEC069457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="688">
   <si>
     <t>Date</t>
   </si>
@@ -180,22 +180,10 @@
     <t>https://www.youtube.com/watch?v=UEWCCSuHsuQ&amp;list=RDUEWCCSuHsuQ&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Patricia Kaas</t>
-  </si>
-  <si>
-    <t>Mademoiselle chante le blues</t>
-  </si>
-  <si>
     <t>Chanson française</t>
   </si>
   <si>
     <t>Voix, piano, orchestre</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Patricia%20Kaas%20Mademoiselle%20chante%20le%20blues</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=g17yeAGwJos</t>
   </si>
   <si>
     <t>Canada</t>
@@ -259,39 +247,18 @@
     <t>https://www.youtube.com/watch?v=JFQ1TSzdpRA&amp;list=RDJFQ1TSzdpRA&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Pomme</t>
-  </si>
-  <si>
-    <t>Grandiose</t>
-  </si>
-  <si>
     <t>Chanson / folk</t>
   </si>
   <si>
     <t>Voix, guitare, piano</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Pomme%20Grandiose</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=jIqA5sg5gZM</t>
-  </si>
-  <si>
     <t>Argentine</t>
   </si>
   <si>
-    <t>Mercedes Sosa</t>
-  </si>
-  <si>
-    <t>Gracias a la Vida</t>
-  </si>
-  <si>
     <t>Folk</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=cIrGQD84F1g&amp;list=RDcIrGQD84F1g&amp;start_radio=1</t>
-  </si>
-  <si>
     <t>Allemagne</t>
   </si>
   <si>
@@ -496,9 +463,6 @@
     <t>Israël</t>
   </si>
   <si>
-    <t>Noa</t>
-  </si>
-  <si>
     <t>Beautiful That Way</t>
   </si>
   <si>
@@ -535,9 +499,6 @@
     <t>Royaume-Uni / Algérie</t>
   </si>
   <si>
-    <t>Sting &amp; Cheb Mami</t>
-  </si>
-  <si>
     <t>Desert Rose</t>
   </si>
   <si>
@@ -670,39 +631,9 @@
     <t>https://www.youtube.com/watch?v=2KPriDj8SYs&amp;list=RD2KPriDj8SYs&amp;start_radio=1</t>
   </si>
   <si>
-    <t>France Gall</t>
-  </si>
-  <si>
-    <t>Ella, elle l’a</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=France%20Gall%20Ella%2C%20elle%20l%E2%80%99a</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=lgHGU8gqz9U</t>
-  </si>
-  <si>
-    <t>France / Belgique</t>
-  </si>
-  <si>
-    <t>Duo mixte</t>
-  </si>
-  <si>
-    <t>Renaud &amp; Axelle Red</t>
-  </si>
-  <si>
-    <t>Manhattan-Kaboul</t>
-  </si>
-  <si>
     <t>Voix, guitare, piano, batterie</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Renaud%20%26%20Axelle%20Red%20Manhattan-Kaboul</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=0qeV8PDBH8E</t>
-  </si>
-  <si>
     <t>Norvège</t>
   </si>
   <si>
@@ -778,9 +709,6 @@
     <t>Ukraine</t>
   </si>
   <si>
-    <t>Estas Tonne feat. Peia</t>
-  </si>
-  <si>
     <t>Bird's Teardrops</t>
   </si>
   <si>
@@ -790,45 +718,9 @@
     <t>https://www.youtube.com/watch?v=hn10okvX19E</t>
   </si>
   <si>
-    <t>Amel Bent</t>
-  </si>
-  <si>
-    <t>Ma philosophie</t>
-  </si>
-  <si>
-    <t>Pop / soul</t>
-  </si>
-  <si>
     <t>Voix, piano, guitare</t>
   </si>
   <si>
-    <t>https://www.youtube.com/results?search_query=Amel%20Bent%20Ma%20philosophie</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=D38EUIll1pM</t>
-  </si>
-  <si>
-    <t>Corée du Sud</t>
-  </si>
-  <si>
-    <t>PSY</t>
-  </si>
-  <si>
-    <t>Gangnam Style</t>
-  </si>
-  <si>
-    <t>K-pop</t>
-  </si>
-  <si>
-    <t>Voix, électronique</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Gangnam+Style+PSY</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=9bZkp7q19f0</t>
-  </si>
-  <si>
     <t>Pologne</t>
   </si>
   <si>
@@ -856,24 +748,9 @@
     <t>https://www.youtube.com/watch?v=7hoyPvEASRg&amp;list=RD7hoyPvEASRg&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Christophe</t>
-  </si>
-  <si>
-    <t>Aline</t>
-  </si>
-  <si>
     <t>Chanson / pop</t>
   </si>
   <si>
-    <t>Voix, piano, guitare, synthétiseur</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Christophe%20Aline</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=seoUs_zFI7c</t>
-  </si>
-  <si>
     <t>Algérie</t>
   </si>
   <si>
@@ -1138,18 +1015,6 @@
     <t>https://www.youtube.com/watch?v=EF1jfbYs3vk&amp;list=RDEF1jfbYs3vk&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Noir Désir</t>
-  </si>
-  <si>
-    <t>Comme elle vient</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=Noir%20D%C3%A9sir%20Comme%20elle%20vient</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=9C9xlKkkeNA</t>
-  </si>
-  <si>
     <t>Mongolie</t>
   </si>
   <si>
@@ -1303,24 +1168,6 @@
     <t>https://www.youtube.com/watch?v=mlbIj2zYLqo</t>
   </si>
   <si>
-    <t>GIMS</t>
-  </si>
-  <si>
-    <t>Sapés comme jamais</t>
-  </si>
-  <si>
-    <t>Rap / pop</t>
-  </si>
-  <si>
-    <t>Voix, beat, synthétiseur</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/results?search_query=GIMS%20Sap%C3%A9s%20comme%20jamais</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=4bPGxLxogvw</t>
-  </si>
-  <si>
     <t>Mali</t>
   </si>
   <si>
@@ -1858,18 +1705,6 @@
     <t>https://www.youtube.com/watch?v=m94_C8Z7wLk&amp;list=RDm94_C8Z7wLk&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Grèce</t>
-  </si>
-  <si>
-    <t>Nana Mouskouri</t>
-  </si>
-  <si>
-    <t>Quand tu chantes</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=b6Ztw1PNvoQ&amp;list=RDb6Ztw1PNvoQ&amp;start_radio=1</t>
-  </si>
-  <si>
     <t>Johannes Brahms</t>
   </si>
   <si>
@@ -2135,6 +1970,128 @@
   </si>
   <si>
     <t>Genres distincts</t>
+  </si>
+  <si>
+    <t>Lisa Leblanc</t>
+  </si>
+  <si>
+    <t>Pourquoi faire aujourd'hui</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RCCmgc9cZVc</t>
+  </si>
+  <si>
+    <t>Oldelaf</t>
+  </si>
+  <si>
+    <t>Les mains froides</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FwaVegAzT84&amp;list=RDFwaVegAzT84&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Wintergatan</t>
+  </si>
+  <si>
+    <t>Suède</t>
+  </si>
+  <si>
+    <t>Proof of Concept</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=m1F7Vl2szd4&amp;list=RDm1F7Vl2szd4&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Achinoam Nini</t>
+  </si>
+  <si>
+    <t>Sting</t>
+  </si>
+  <si>
+    <t>Sanseverino</t>
+  </si>
+  <si>
+    <t>Maigrir</t>
+  </si>
+  <si>
+    <t>Jazz Manouche</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VizjETIFsjs</t>
+  </si>
+  <si>
+    <t>Boney M.</t>
+  </si>
+  <si>
+    <t>Daddy Cool</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FYGTT7YhywA</t>
+  </si>
+  <si>
+    <t>Estas Tonne</t>
+  </si>
+  <si>
+    <t>Chanson Pour Les Amis</t>
+  </si>
+  <si>
+    <t>Miossec</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wwG_F5Ct4e4&amp;list=RDwwG_F5Ct4e4&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>The Michael Zager Band</t>
+  </si>
+  <si>
+    <t>Let's All Chant</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PmzxG9kdZhM&amp;list=RDPmzxG9kdZhM&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Pow Wow</t>
+  </si>
+  <si>
+    <t>Le lion est mort ce soir</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xb3mhXCsBJg&amp;list=RDxb3mhXCsBJg&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Jardin d'hiver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Henri Salvador</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lNZIzor29LI&amp;list=RDlNZIzor29LI&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Cerrone</t>
+  </si>
+  <si>
+    <t>Supernature</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OPsPmi35OeY&amp;list=RDOPsPmi35OeY&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Lucky Chops</t>
+  </si>
+  <si>
+    <t>Danza</t>
+  </si>
+  <si>
+    <t>Fanfare</t>
+  </si>
+  <si>
+    <t>Cuivres, Vent</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ddijvwAMw0o&amp;list=RDddijvwAMw0o&amp;start_radio=1</t>
   </si>
 </sst>
 </file>
@@ -2732,39 +2689,37 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46275</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3">
-        <v>1987</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>55</v>
+        <v>650</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>56</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2775,31 +2730,31 @@
         <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3">
         <v>2019</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="K8" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2810,7 +2765,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D9" s="3">
         <v>1962</v>
@@ -2819,22 +2774,22 @@
         <v>37</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2851,25 +2806,25 @@
         <v>1986</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2883,28 +2838,26 @@
         <v>21</v>
       </c>
       <c r="D11" s="3">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>651</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>78</v>
+        <v>652</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>80</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>81</v>
+        <v>653</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>82</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2912,34 +2865,32 @@
         <v>46283</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>83</v>
+        <v>655</v>
       </c>
       <c r="D12" s="3">
-        <v>1971</v>
+        <v>2019</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>654</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>85</v>
+        <v>656</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>87</v>
+        <v>657</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>87</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -2950,7 +2901,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3">
         <v>1761</v>
@@ -2959,22 +2910,22 @@
         <v>37</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2985,7 +2936,7 @@
         <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3">
         <v>2000</v>
@@ -2994,22 +2945,22 @@
         <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3026,25 +2977,25 @@
         <v>1998</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3052,34 +3003,34 @@
         <v>46290</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D16" s="3">
         <v>2014</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3090,7 +3041,7 @@
         <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D17" s="3">
         <v>1786</v>
@@ -3099,22 +3050,22 @@
         <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3122,10 +3073,10 @@
         <v>46294</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D18" s="3">
         <v>2007</v>
@@ -3134,22 +3085,22 @@
         <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3169,22 +3120,22 @@
         <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3192,10 +3143,10 @@
         <v>46297</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D20" s="3">
         <v>2015</v>
@@ -3204,22 +3155,22 @@
         <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3239,22 +3190,22 @@
         <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3262,34 +3213,34 @@
         <v>46301</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D22" s="3">
         <v>1998</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3309,22 +3260,22 @@
         <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3335,7 +3286,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D24" s="3">
         <v>1999</v>
@@ -3344,22 +3295,22 @@
         <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>156</v>
+        <v>658</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3370,7 +3321,7 @@
         <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D25" s="3">
         <v>1853</v>
@@ -3379,22 +3330,22 @@
         <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3402,34 +3353,34 @@
         <v>46308</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D26" s="3">
         <v>2000</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>169</v>
+        <v>659</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3446,25 +3397,25 @@
         <v>2002</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3472,34 +3423,34 @@
         <v>46311</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D28" s="3">
         <v>1994</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3510,7 +3461,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D29" s="3">
         <v>1915</v>
@@ -3519,10 +3470,10 @@
         <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>40</v>
@@ -3531,10 +3482,10 @@
         <v>41</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3545,7 +3496,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D30" s="3">
         <v>1990</v>
@@ -3554,22 +3505,22 @@
         <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3586,25 +3537,25 @@
         <v>2009</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3624,22 +3575,22 @@
         <v>37</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -3650,7 +3601,7 @@
         <v>20</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D33" s="3">
         <v>1725</v>
@@ -3659,22 +3610,22 @@
         <v>37</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3685,7 +3636,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3">
         <v>1999</v>
@@ -3694,25 +3645,25 @@
         <v>37</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>46338</v>
       </c>
@@ -3723,31 +3674,31 @@
         <v>21</v>
       </c>
       <c r="D35" s="3">
-        <v>1987</v>
+        <v>2002</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>660</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>215</v>
+        <v>661</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>97</v>
+        <v>662</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>663</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>46339</v>
       </c>
@@ -3755,31 +3706,31 @@
         <v>20</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3">
-        <v>2002</v>
+        <v>1976</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>219</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>220</v>
+        <v>664</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>221</v>
+        <v>665</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>223</v>
+        <v>666</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>224</v>
+        <v>666</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3790,7 +3741,7 @@
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="D37" s="3">
         <v>1875</v>
@@ -3799,22 +3750,22 @@
         <v>37</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3834,22 +3785,22 @@
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3866,25 +3817,25 @@
         <v>2014</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3895,7 +3846,7 @@
         <v>35</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="D40" s="3">
         <v>2013</v>
@@ -3904,22 +3855,22 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -3939,22 +3890,22 @@
         <v>37</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -3965,31 +3916,31 @@
         <v>20</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="D42" s="3">
         <v>2018</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>250</v>
+        <v>667</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4003,28 +3954,26 @@
         <v>21</v>
       </c>
       <c r="D43" s="3">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>254</v>
+        <v>669</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>255</v>
+        <v>668</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>257</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>258</v>
+        <v>670</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>259</v>
+        <v>670</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4035,31 +3984,29 @@
         <v>43</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>2012</v>
+        <v>1978</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>261</v>
+        <v>671</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>262</v>
+        <v>672</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>264</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>265</v>
+        <v>673</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>266</v>
+        <v>673</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4070,7 +4017,7 @@
         <v>20</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="D45" s="3">
         <v>1834</v>
@@ -4079,22 +4026,22 @@
         <v>37</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4105,7 +4052,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D46" s="3">
         <v>1988</v>
@@ -4114,22 +4061,22 @@
         <v>37</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4143,28 +4090,28 @@
         <v>21</v>
       </c>
       <c r="D47" s="3">
-        <v>1965</v>
+        <v>1992</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>276</v>
+        <v>674</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>277</v>
+        <v>675</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>279</v>
+        <v>70</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>280</v>
+        <v>676</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>281</v>
+        <v>676</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4175,31 +4122,31 @@
         <v>27</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
       <c r="D48" s="3">
         <v>1993</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>285</v>
+        <v>244</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4210,7 +4157,7 @@
         <v>20</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D49" s="3">
         <v>1876</v>
@@ -4219,22 +4166,22 @@
         <v>37</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4242,10 +4189,10 @@
         <v>46364</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D50" s="3">
         <v>2011</v>
@@ -4254,22 +4201,22 @@
         <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4286,25 +4233,25 @@
         <v>1982</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4312,10 +4259,10 @@
         <v>46367</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D52" s="3">
         <v>2013</v>
@@ -4324,22 +4271,22 @@
         <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4350,7 +4297,7 @@
         <v>20</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D53" s="3">
         <v>1741</v>
@@ -4359,22 +4306,22 @@
         <v>37</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>308</v>
+        <v>267</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4385,7 +4332,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="D54" s="3">
         <v>1993</v>
@@ -4394,22 +4341,22 @@
         <v>13</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4429,22 +4376,22 @@
         <v>37</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4461,25 +4408,25 @@
         <v>1984</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4490,7 +4437,7 @@
         <v>20</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D57" s="3">
         <v>1926</v>
@@ -4499,22 +4446,22 @@
         <v>37</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>325</v>
+        <v>284</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4525,7 +4472,7 @@
         <v>43</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D58" s="3">
         <v>2005</v>
@@ -4534,22 +4481,22 @@
         <v>13</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>331</v>
+        <v>290</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>332</v>
+        <v>291</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>333</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4566,25 +4513,25 @@
         <v>1960</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>334</v>
+        <v>293</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>335</v>
+        <v>294</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>338</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4601,25 +4548,25 @@
         <v>1988</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>342</v>
+        <v>301</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4630,7 +4577,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="D61" s="3">
         <v>1893</v>
@@ -4639,22 +4586,22 @@
         <v>37</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4665,7 +4612,7 @@
         <v>27</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="D62" s="3">
         <v>1972</v>
@@ -4674,22 +4621,22 @@
         <v>37</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4709,22 +4656,22 @@
         <v>13</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4735,7 +4682,7 @@
         <v>27</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="D64" s="3">
         <v>1986</v>
@@ -4744,22 +4691,22 @@
         <v>37</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>361</v>
+        <v>320</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>362</v>
+        <v>321</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4770,7 +4717,7 @@
         <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D65" s="3">
         <v>1788</v>
@@ -4779,22 +4726,22 @@
         <v>37</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4811,25 +4758,25 @@
         <v>1998</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4843,28 +4790,28 @@
         <v>21</v>
       </c>
       <c r="D67" s="3">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>370</v>
+        <v>678</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>371</v>
+        <v>677</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>372</v>
+        <v>679</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>373</v>
+        <v>679</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4875,7 +4822,7 @@
         <v>43</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="D68" s="3">
         <v>2014</v>
@@ -4884,22 +4831,22 @@
         <v>37</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>379</v>
+        <v>334</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>380</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4919,10 +4866,10 @@
         <v>37</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>381</v>
+        <v>336</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>40</v>
@@ -4931,10 +4878,10 @@
         <v>41</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>384</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4945,31 +4892,31 @@
         <v>20</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D70" s="3">
         <v>1978</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>390</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4989,22 +4936,22 @@
         <v>37</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>394</v>
+        <v>349</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>395</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5024,10 +4971,10 @@
         <v>13</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>16</v>
@@ -5036,10 +4983,10 @@
         <v>25</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>399</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5050,7 +4997,7 @@
         <v>20</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D73" s="3">
         <v>1892</v>
@@ -5059,22 +5006,22 @@
         <v>37</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>401</v>
+        <v>356</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5085,7 +5032,7 @@
         <v>27</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="D74" s="3">
         <v>1974</v>
@@ -5094,22 +5041,22 @@
         <v>37</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>404</v>
+        <v>359</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>409</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5126,25 +5073,25 @@
         <v>1955</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5152,10 +5099,10 @@
         <v>46423</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D76" s="3">
         <v>2013</v>
@@ -5164,22 +5111,22 @@
         <v>37</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>413</v>
+        <v>368</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>414</v>
+        <v>369</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -5190,7 +5137,7 @@
         <v>20</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D77" s="3">
         <v>1725</v>
@@ -5199,22 +5146,22 @@
         <v>37</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>420</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5228,28 +5175,26 @@
         <v>21</v>
       </c>
       <c r="D78" s="3">
-        <v>2020</v>
+        <v>1977</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>421</v>
+        <v>680</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>422</v>
+        <v>681</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>80</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>423</v>
+        <v>682</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>424</v>
+        <v>682</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5263,28 +5208,28 @@
         <v>21</v>
       </c>
       <c r="D79" s="3">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>427</v>
+        <v>51</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>428</v>
+        <v>74</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>430</v>
+        <v>379</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5295,31 +5240,31 @@
         <v>27</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="D80" s="3">
         <v>2017</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>436</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5330,7 +5275,7 @@
         <v>20</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D81" s="3">
         <v>1808</v>
@@ -5339,22 +5284,22 @@
         <v>37</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5371,25 +5316,25 @@
         <v>1966</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -5406,25 +5351,25 @@
         <v>1997</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5435,7 +5380,7 @@
         <v>35</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D84" s="3">
         <v>1995</v>
@@ -5444,22 +5389,22 @@
         <v>13</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>452</v>
+        <v>401</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -5479,22 +5424,22 @@
         <v>37</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5505,7 +5450,7 @@
         <v>43</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D86" s="3">
         <v>1998</v>
@@ -5514,22 +5459,22 @@
         <v>13</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>455</v>
+        <v>404</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>456</v>
+        <v>405</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>457</v>
+        <v>406</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -5549,22 +5494,22 @@
         <v>37</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>460</v>
+        <v>409</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>463</v>
+        <v>412</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5575,7 +5520,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="D88" s="3">
         <v>2005</v>
@@ -5584,10 +5529,10 @@
         <v>37</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>24</v>
@@ -5596,10 +5541,10 @@
         <v>17</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>469</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5610,7 +5555,7 @@
         <v>20</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D89" s="3">
         <v>1825</v>
@@ -5619,22 +5564,22 @@
         <v>37</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>470</v>
+        <v>419</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>472</v>
+        <v>421</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>472</v>
+        <v>421</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5654,22 +5599,22 @@
         <v>37</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>473</v>
+        <v>422</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5689,22 +5634,22 @@
         <v>13</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>478</v>
+        <v>427</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>479</v>
+        <v>428</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>480</v>
+        <v>429</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>481</v>
+        <v>430</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5715,31 +5660,31 @@
         <v>20</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D92" s="3">
         <v>1977</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>485</v>
+        <v>434</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>486</v>
+        <v>435</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>486</v>
+        <v>435</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5750,7 +5695,7 @@
         <v>20</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D93" s="3">
         <v>1888</v>
@@ -5759,22 +5704,22 @@
         <v>37</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>487</v>
+        <v>436</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>488</v>
+        <v>437</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>489</v>
+        <v>438</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>489</v>
+        <v>438</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5785,7 +5730,7 @@
         <v>27</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="D94" s="3">
         <v>2021</v>
@@ -5794,22 +5739,22 @@
         <v>37</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>490</v>
+        <v>439</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5826,25 +5771,25 @@
         <v>2017</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>496</v>
+        <v>445</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>498</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5855,7 +5800,7 @@
         <v>43</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D96" s="3">
         <v>2008</v>
@@ -5864,22 +5809,22 @@
         <v>37</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>499</v>
+        <v>448</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>500</v>
+        <v>449</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>501</v>
+        <v>450</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>501</v>
+        <v>450</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -5890,7 +5835,7 @@
         <v>20</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D97" s="3">
         <v>1723</v>
@@ -5899,22 +5844,22 @@
         <v>37</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>502</v>
+        <v>451</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>504</v>
+        <v>453</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>505</v>
+        <v>454</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5925,7 +5870,7 @@
         <v>20</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="D98" s="3">
         <v>2025</v>
@@ -5934,10 +5879,10 @@
         <v>13</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>506</v>
+        <v>455</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>507</v>
+        <v>456</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>31</v>
@@ -5946,10 +5891,10 @@
         <v>32</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5969,10 +5914,10 @@
         <v>37</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>24</v>
@@ -5981,10 +5926,10 @@
         <v>17</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6004,22 +5949,22 @@
         <v>13</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>511</v>
+        <v>460</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>512</v>
+        <v>461</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>513</v>
+        <v>462</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>514</v>
+        <v>463</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>515</v>
+        <v>464</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6036,25 +5981,25 @@
         <v>1963</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>516</v>
+        <v>465</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>517</v>
+        <v>466</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>518</v>
+        <v>467</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>519</v>
+        <v>468</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>520</v>
+        <v>469</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6074,22 +6019,22 @@
         <v>13</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>521</v>
+        <v>470</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>522</v>
+        <v>471</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>523</v>
+        <v>472</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>524</v>
+        <v>473</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6100,31 +6045,31 @@
         <v>35</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>525</v>
+        <v>474</v>
       </c>
       <c r="D103" s="3">
         <v>1997</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>526</v>
+        <v>475</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>527</v>
+        <v>476</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>528</v>
+        <v>477</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>529</v>
+        <v>478</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>530</v>
+        <v>479</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -6135,7 +6080,7 @@
         <v>20</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D104" s="3">
         <v>1791</v>
@@ -6144,22 +6089,22 @@
         <v>37</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>531</v>
+        <v>480</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>532</v>
+        <v>481</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>533</v>
+        <v>482</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6170,7 +6115,7 @@
         <v>43</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D105" s="3">
         <v>1985</v>
@@ -6179,22 +6124,22 @@
         <v>37</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>534</v>
+        <v>483</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>535</v>
+        <v>484</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>536</v>
+        <v>485</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>537</v>
+        <v>486</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>538</v>
+        <v>487</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>538</v>
+        <v>487</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6211,25 +6156,25 @@
         <v>2003</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>539</v>
+        <v>488</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>541</v>
+        <v>490</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>542</v>
+        <v>491</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6237,10 +6182,10 @@
         <v>46493</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D107" s="3">
         <v>2004</v>
@@ -6249,22 +6194,22 @@
         <v>37</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>543</v>
+        <v>492</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>544</v>
+        <v>493</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>546</v>
+        <v>495</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>547</v>
+        <v>496</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>547</v>
+        <v>496</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6275,7 +6220,7 @@
         <v>20</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="D108" s="3">
         <v>1839</v>
@@ -6284,22 +6229,22 @@
         <v>37</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>548</v>
+        <v>497</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>549</v>
+        <v>498</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>549</v>
+        <v>498</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6310,31 +6255,31 @@
         <v>20</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D109" s="3">
         <v>1985</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>552</v>
+        <v>501</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>553</v>
+        <v>502</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6345,7 +6290,7 @@
         <v>20</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D110" s="3">
         <v>1843</v>
@@ -6354,22 +6299,22 @@
         <v>37</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>555</v>
+        <v>504</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>556</v>
+        <v>505</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>556</v>
+        <v>505</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6380,7 +6325,7 @@
         <v>20</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>557</v>
+        <v>506</v>
       </c>
       <c r="D111" s="3">
         <v>2019</v>
@@ -6389,22 +6334,22 @@
         <v>13</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>558</v>
+        <v>507</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>559</v>
+        <v>508</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>560</v>
+        <v>509</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>561</v>
+        <v>510</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6424,22 +6369,22 @@
         <v>37</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>562</v>
+        <v>511</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>563</v>
+        <v>512</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>564</v>
+        <v>513</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6450,7 +6395,7 @@
         <v>20</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>565</v>
+        <v>514</v>
       </c>
       <c r="D113" s="3">
         <v>1997</v>
@@ -6459,22 +6404,22 @@
         <v>13</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>566</v>
+        <v>515</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>569</v>
+        <v>518</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>570</v>
+        <v>519</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>571</v>
+        <v>520</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6491,25 +6436,25 @@
         <v>1981</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>572</v>
+        <v>521</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>573</v>
+        <v>522</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>574</v>
+        <v>523</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>574</v>
+        <v>523</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6529,22 +6474,22 @@
         <v>13</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>575</v>
+        <v>524</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>576</v>
+        <v>525</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>577</v>
+        <v>526</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>578</v>
+        <v>527</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>579</v>
+        <v>528</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6555,7 +6500,7 @@
         <v>11</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D116" s="3">
         <v>1974</v>
@@ -6564,22 +6509,22 @@
         <v>37</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>580</v>
+        <v>529</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>581</v>
+        <v>530</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>582</v>
+        <v>531</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>583</v>
+        <v>532</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>584</v>
+        <v>533</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>584</v>
+        <v>533</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6590,7 +6535,7 @@
         <v>20</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D117" s="3">
         <v>1869</v>
@@ -6599,22 +6544,22 @@
         <v>37</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>585</v>
+        <v>534</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>586</v>
+        <v>535</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>587</v>
+        <v>536</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>587</v>
+        <v>536</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6625,7 +6570,7 @@
         <v>43</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="D118" s="3">
         <v>1983</v>
@@ -6634,22 +6579,22 @@
         <v>37</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>588</v>
+        <v>537</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>589</v>
+        <v>538</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>590</v>
+        <v>539</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>590</v>
+        <v>539</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6666,25 +6611,25 @@
         <v>2007</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>591</v>
+        <v>540</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>592</v>
+        <v>541</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>593</v>
+        <v>542</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>594</v>
+        <v>543</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6701,25 +6646,25 @@
         <v>2012</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>595</v>
+        <v>544</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>596</v>
+        <v>545</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>597</v>
+        <v>546</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>598</v>
+        <v>547</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6739,22 +6684,22 @@
         <v>37</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>600</v>
+        <v>549</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>601</v>
+        <v>550</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>601</v>
+        <v>550</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6765,7 +6710,7 @@
         <v>20</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D122" s="3">
         <v>2013</v>
@@ -6774,22 +6719,22 @@
         <v>37</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>602</v>
+        <v>551</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>603</v>
+        <v>552</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>604</v>
+        <v>553</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>605</v>
+        <v>554</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6809,22 +6754,22 @@
         <v>13</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>606</v>
+        <v>555</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>607</v>
+        <v>556</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>608</v>
+        <v>557</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>609</v>
+        <v>558</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>609</v>
+        <v>558</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6835,31 +6780,31 @@
         <v>20</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>610</v>
+        <v>231</v>
       </c>
       <c r="D124" s="3">
-        <v>1975</v>
+        <v>2001</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>53</v>
+        <v>169</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6870,7 +6815,7 @@
         <v>20</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D125" s="3">
         <v>1868</v>
@@ -6879,22 +6824,22 @@
         <v>37</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>614</v>
+        <v>559</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>615</v>
+        <v>560</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>616</v>
+        <v>561</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>617</v>
+        <v>562</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>617</v>
+        <v>562</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6914,22 +6859,22 @@
         <v>13</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>618</v>
+        <v>563</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>619</v>
+        <v>564</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>620</v>
+        <v>565</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>621</v>
+        <v>566</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>622</v>
+        <v>567</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6949,22 +6894,22 @@
         <v>37</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>623</v>
+        <v>568</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>623</v>
+        <v>568</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -6972,10 +6917,10 @@
         <v>46549</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D128" s="3">
         <v>2013</v>
@@ -6984,22 +6929,22 @@
         <v>37</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>624</v>
+        <v>569</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>625</v>
+        <v>570</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>627</v>
+        <v>572</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>628</v>
+        <v>573</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>628</v>
+        <v>573</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -7019,22 +6964,22 @@
         <v>37</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>629</v>
+        <v>574</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>630</v>
+        <v>575</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>631</v>
+        <v>576</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>632</v>
+        <v>577</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7045,7 +6990,7 @@
         <v>20</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D130" s="3">
         <v>1973</v>
@@ -7054,22 +6999,22 @@
         <v>37</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>633</v>
+        <v>578</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>634</v>
+        <v>579</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>635</v>
+        <v>580</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>636</v>
+        <v>581</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>637</v>
+        <v>582</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7086,25 +7031,25 @@
         <v>2006</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>638</v>
+        <v>583</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>639</v>
+        <v>584</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>640</v>
+        <v>585</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>640</v>
+        <v>585</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7121,13 +7066,13 @@
         <v>1958</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>641</v>
+        <v>586</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>642</v>
+        <v>587</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>16</v>
@@ -7136,10 +7081,10 @@
         <v>17</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>643</v>
+        <v>588</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>643</v>
+        <v>588</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7159,22 +7104,22 @@
         <v>37</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>644</v>
+        <v>589</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>645</v>
+        <v>590</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>646</v>
+        <v>591</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>647</v>
+        <v>592</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7194,22 +7139,22 @@
         <v>13</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>648</v>
+        <v>593</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>649</v>
+        <v>594</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>652</v>
+        <v>597</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7229,22 +7174,22 @@
         <v>13</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>653</v>
+        <v>598</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>654</v>
+        <v>599</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>655</v>
+        <v>600</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>656</v>
+        <v>601</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>656</v>
+        <v>601</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7264,22 +7209,22 @@
         <v>13</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>657</v>
+        <v>602</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>659</v>
+        <v>604</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>660</v>
+        <v>605</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>660</v>
+        <v>605</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -7290,7 +7235,7 @@
         <v>20</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D137" s="3">
         <v>1824</v>
@@ -7299,22 +7244,22 @@
         <v>37</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>661</v>
+        <v>606</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>662</v>
+        <v>607</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>663</v>
+        <v>608</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>664</v>
+        <v>609</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7325,31 +7270,31 @@
         <v>20</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="D138" s="3">
         <v>1996</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>665</v>
+        <v>610</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>666</v>
+        <v>611</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>667</v>
+        <v>612</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>668</v>
+        <v>613</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>669</v>
+        <v>614</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7366,25 +7311,25 @@
         <v>2003</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>670</v>
+        <v>615</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>671</v>
+        <v>616</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>672</v>
+        <v>617</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7392,34 +7337,34 @@
         <v>46570</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="D140" s="3">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>182</v>
+        <v>685</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -7449,16 +7394,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>678</v>
+        <v>623</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>679</v>
+        <v>624</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>680</v>
+        <v>625</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>681</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -7548,7 +7493,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -7565,7 +7510,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7582,7 +7527,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -7599,7 +7544,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -7616,7 +7561,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -7647,47 +7592,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>682</v>
+        <v>627</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>683</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>684</v>
+        <v>629</v>
       </c>
       <c r="B2" t="s">
-        <v>685</v>
+        <v>630</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>686</v>
+        <v>631</v>
       </c>
       <c r="B3" t="s">
-        <v>687</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>688</v>
+        <v>633</v>
       </c>
       <c r="B4" t="s">
-        <v>689</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>690</v>
+        <v>635</v>
       </c>
       <c r="B5" t="s">
-        <v>691</v>
+        <v>636</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>692</v>
+        <v>637</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7695,23 +7640,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>693</v>
+        <v>638</v>
       </c>
       <c r="B7" t="s">
-        <v>694</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>695</v>
+        <v>640</v>
       </c>
       <c r="B8" t="s">
-        <v>696</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>697</v>
+        <v>642</v>
       </c>
       <c r="B9">
         <v>139</v>
@@ -7719,7 +7664,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>698</v>
+        <v>643</v>
       </c>
       <c r="B10">
         <v>33</v>
@@ -7727,7 +7672,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>699</v>
+        <v>644</v>
       </c>
       <c r="B11">
         <v>36</v>
@@ -7735,7 +7680,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>700</v>
+        <v>645</v>
       </c>
       <c r="B12">
         <v>35</v>
@@ -7743,7 +7688,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>701</v>
+        <v>646</v>
       </c>
       <c r="B13">
         <v>35</v>
@@ -7751,7 +7696,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>678</v>
+        <v>623</v>
       </c>
       <c r="B14">
         <v>64</v>
@@ -7759,7 +7704,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>679</v>
+        <v>624</v>
       </c>
       <c r="B15">
         <v>36</v>
@@ -7767,7 +7712,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>680</v>
+        <v>625</v>
       </c>
       <c r="B16">
         <v>39</v>
@@ -7775,7 +7720,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>702</v>
+        <v>647</v>
       </c>
       <c r="B17">
         <v>57</v>

--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DFA5D8-4BE0-F94F-9EA4-ADAEC069457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FC7E71-2A1B-AC48-8FA0-CED940FCA92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2050,9 +2050,6 @@
     <t>https://www.youtube.com/watch?v=PmzxG9kdZhM&amp;list=RDPmzxG9kdZhM&amp;start_radio=1</t>
   </si>
   <si>
-    <t>Pow Wow</t>
-  </si>
-  <si>
     <t>Le lion est mort ce soir</t>
   </si>
   <si>
@@ -2092,6 +2089,9 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=ddijvwAMw0o&amp;list=RDddijvwAMw0o&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Pow Wow (groupe)</t>
   </si>
 </sst>
 </file>
@@ -4096,10 +4096,10 @@
         <v>37</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>675</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>240</v>
@@ -4108,10 +4108,10 @@
         <v>70</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4796,10 +4796,10 @@
         <v>37</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>118</v>
@@ -4808,10 +4808,10 @@
         <v>257</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5181,20 +5181,20 @@
         <v>37</v>
       </c>
       <c r="F78" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="G78" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>681</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>86</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -7349,22 +7349,22 @@
         <v>66</v>
       </c>
       <c r="F140" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="G140" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="H140" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="H140" s="3" t="s">
+      <c r="I140" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="I140" s="3" t="s">
+      <c r="J140" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="J140" s="3" t="s">
-        <v>687</v>
-      </c>
       <c r="K140" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
